--- a/excel/3. Perturbation 10.xlsx
+++ b/excel/3. Perturbation 10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\2. Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\git\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F27CC3-0A09-448E-A328-4206A3A530E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A648E34-E672-4276-84E5-508853104C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{88C08D68-2E9A-4EC7-8AF8-2F1D08621B1E}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{88C08D68-2E9A-4EC7-8AF8-2F1D08621B1E}"/>
   </bookViews>
   <sheets>
     <sheet name="cnt" sheetId="6" r:id="rId1"/>
@@ -442,7 +442,7 @@
     <t>Perturbation</t>
   </si>
   <si>
-    <t>Alpha-10% &amp; Beta+10% but capped at 0 and 1 respectively</t>
+    <t>lower bounds -10% &amp; upper bounds +10% but capped at 0 and 1 respectively</t>
   </si>
 </sst>
 </file>
@@ -554,7 +554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -974,21 +974,6 @@
         <color indexed="64"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color rgb="FFD6DADC"/>
       </right>
       <top style="medium">
@@ -1263,81 +1248,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FFFF0000"/>
       </left>
@@ -1382,11 +1292,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1525,7 +1450,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1548,7 +1472,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1566,7 +1490,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1578,7 +1502,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1590,22 +1514,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1614,7 +1538,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1638,13 +1562,13 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
@@ -1652,38 +1576,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1729,6 +1637,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1962,28 +1877,28 @@
                   <c:v>MailNews Core</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Mozilla QA</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>NSS</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Release Engineering</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Remote Protocol</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>support.mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>WebExtensions</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Webtools</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Mozilla QA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1995,52 +1910,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>8.3172790190607054E-2</c:v>
+                  <c:v>9.0087567627719273E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.24575998045477201</c:v>
+                  <c:v>0.24218364672994513</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4237926084646286E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.10153161199411295</c:v>
+                  <c:v>9.3693833971625687E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.15798487598078384</c:v>
+                  <c:v>0.17281514423369421</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.6238363263861408E-2</c:v>
+                  <c:v>6.9904434897755066E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.5628966363617819E-2</c:v>
+                  <c:v>1.8938481781315832E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.1915998463009528E-3</c:v>
+                  <c:v>3.2179592795721075E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.21553745845217631</c:v>
+                  <c:v>0.13281592687881044</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.22912018450928701</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.11722471993809447</c:v>
+                  <c:v>3.6790692487628017E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.6204488053538518E-2</c:v>
+                  <c:v>0.1155262013396313</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.10770383827125189</c:v>
+                  <c:v>5.6798854511208419E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.209618231965944E-2</c:v>
+                  <c:v>9.373295214564735E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.3150115211214303E-2</c:v>
+                  <c:v>1.9749932848463825E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.14996919272347622</c:v>
+                  <c:v>4.5961547367092896E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2098,7 +2013,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D4275699-7CFC-40A1-829F-BF8DF07EC68F}" type="CELLRANGE">
+                    <a:fld id="{AB83A80D-4392-4B19-8874-0C9127E157C7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2130,7 +2045,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{97F87AF1-A1DD-4FBD-BDE2-7114005B3E6C}" type="CELLRANGE">
+                    <a:fld id="{F97FC766-BCBF-4C3B-94DC-8AE9F5A4FDDF}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2163,7 +2078,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{90738539-044F-4946-B02C-94CB057191B1}" type="CELLRANGE">
+                    <a:fld id="{369582B6-AADD-4F7F-918A-30D8328E3633}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2196,7 +2111,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{00D4AB22-AFBC-4C18-AE76-B5F9A3222B10}" type="CELLRANGE">
+                    <a:fld id="{B1DFB84A-2FFB-4536-9D50-642083B8584F}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2229,7 +2144,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B22FF760-C14F-4BB3-B94C-B2C9F31E58B1}" type="CELLRANGE">
+                    <a:fld id="{A7F5761B-5274-4F92-B47B-CA9CEFBDAE42}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2262,7 +2177,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0EA68A83-BB67-441F-B8A4-2156EE70FA65}" type="CELLRANGE">
+                    <a:fld id="{F644037F-654E-4414-97C5-E02FA286E077}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2295,7 +2210,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A1DEFF4E-E4B5-48FF-85B9-ED46DD46F8AA}" type="CELLRANGE">
+                    <a:fld id="{C44BB05C-D4AA-407C-B880-1DF8CE0240DA}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2328,7 +2243,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BDE23DF1-2B21-41E8-A745-93753292DBD0}" type="CELLRANGE">
+                    <a:fld id="{3C32F01F-491A-40A6-956E-8025F0B68A4A}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2361,7 +2276,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD5DA881-C74A-435B-A4C8-03198F11A78C}" type="CELLRANGE">
+                    <a:fld id="{F8A93923-CA54-4CE2-ACD6-A40FBB37E204}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2394,7 +2309,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{94590A19-B0AC-411B-BA3E-30206EADF1FE}" type="CELLRANGE">
+                    <a:fld id="{637DE902-AC78-447D-ADB7-4543C19070B1}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2427,7 +2342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E6DD74B7-C8F4-44EF-9D5E-5A1E13B8A623}" type="CELLRANGE">
+                    <a:fld id="{021B56EC-248B-49CE-83BF-A3F7F52322D5}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2460,7 +2375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9FF938F1-7A9F-4A7B-9DE7-1E3F671DBFE9}" type="CELLRANGE">
+                    <a:fld id="{3E101DAF-F15C-40B3-9D05-71B53C6FA8C0}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2493,7 +2408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C0519F81-EA4B-429E-BE3E-8751892689ED}" type="CELLRANGE">
+                    <a:fld id="{F593C0F1-6B9A-4072-A730-719B5A8C968A}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2526,7 +2441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{457819CD-3FF4-4055-A07F-06D59310CB86}" type="CELLRANGE">
+                    <a:fld id="{51B84F85-5093-480B-83BA-020CC19A371F}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2559,7 +2474,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5AA664EA-4B11-49A8-A5CD-40CC3583B045}" type="CELLRANGE">
+                    <a:fld id="{0A9C8A59-18AD-4E2D-BDDB-EADC1A580EF9}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2592,7 +2507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BD857521-5DED-49BD-B334-DA5F98695ACA}" type="CELLRANGE">
+                    <a:fld id="{10019792-1330-4DCB-BD08-888C8C4D30B3}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2705,28 +2620,28 @@
                   <c:v>MailNews Core</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Mozilla QA</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>NSS</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Release Engineering</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Remote Protocol</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>support.mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>WebExtensions</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Webtools</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Mozilla QA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2738,52 +2653,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.78296409412688073</c:v>
+                  <c:v>0.71222889661843003</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.61708519987635002</c:v>
+                  <c:v>0.45555129390971016</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73147521138449001</c:v>
+                  <c:v>0.60907647296738576</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.79864369502718369</c:v>
+                  <c:v>0.70528474990662582</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6931427988359915</c:v>
+                  <c:v>0.55689539058513748</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77736138052996484</c:v>
+                  <c:v>0.71784517625153765</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.72043781053215594</c:v>
+                  <c:v>0.63188736481267072</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.77480086852357211</c:v>
+                  <c:v>0.7356598487592525</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.79144314246005465</c:v>
+                  <c:v>0.63966674660775447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.77994550273956109</c:v>
+                  <c:v>0.76587215139716669</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.70375400617091488</c:v>
+                  <c:v>0.68439642511828269</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.73535070604319641</c:v>
+                  <c:v>0.58432829108518969</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.8052922312867391</c:v>
+                  <c:v>0.61034934480734138</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.66805795471019902</c:v>
+                  <c:v>0.76638711088729661</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82134233398485135</c:v>
+                  <c:v>0.51615494853592514</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2796,52 +2711,52 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="16"/>
                   <c:pt idx="0">
-                    <c:v>0.783</c:v>
+                    <c:v>0.712</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>1.000</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>0.617</c:v>
+                    <c:v>0.456</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>0.731</c:v>
+                    <c:v>0.609</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.799</c:v>
+                    <c:v>0.705</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0.693</c:v>
+                    <c:v>0.557</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>0.777</c:v>
+                    <c:v>0.718</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>0.720</c:v>
+                    <c:v>0.632</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>0.775</c:v>
+                    <c:v>0.736</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>0.791</c:v>
+                    <c:v>0.640</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>0.780</c:v>
+                    <c:v>0.766</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>0.704</c:v>
+                    <c:v>0.684</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>0.735</c:v>
+                    <c:v>0.584</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>0.805</c:v>
+                    <c:v>0.610</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>0.668</c:v>
+                    <c:v>0.766</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>0.821</c:v>
+                    <c:v>0.516</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -4012,26 +3927,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="66"/>
-      <c r="C1" s="66" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="20"/>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="61" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4042,10 +3957,10 @@
       <c r="C4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="62">
         <v>45170</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="62">
         <v>45199</v>
       </c>
       <c r="F4" s="8">
@@ -4059,10 +3974,10 @@
       <c r="C5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="62">
         <v>45200</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="62">
         <v>45230</v>
       </c>
       <c r="F5" s="8">
@@ -4076,10 +3991,10 @@
       <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="62">
         <v>45231</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="62">
         <v>45260</v>
       </c>
       <c r="F6" s="8">
@@ -4093,10 +4008,10 @@
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="62">
         <v>45261</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="62">
         <v>45291</v>
       </c>
       <c r="F7" s="8">
@@ -4110,10 +4025,10 @@
       <c r="C8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="62">
         <v>45292</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="62">
         <v>45322</v>
       </c>
       <c r="F8" s="8">
@@ -4127,10 +4042,10 @@
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="62">
         <v>45323</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="62">
         <v>45351</v>
       </c>
       <c r="F9" s="8">
@@ -4144,10 +4059,10 @@
       <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="62">
         <v>45352</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="62">
         <v>45382</v>
       </c>
       <c r="F10" s="8">
@@ -4161,10 +4076,10 @@
       <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="62">
         <v>45383</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="62">
         <v>45412</v>
       </c>
       <c r="F11" s="8">
@@ -4178,10 +4093,10 @@
       <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="62">
         <v>45413</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="62">
         <v>45443</v>
       </c>
       <c r="F12" s="8">
@@ -4195,10 +4110,10 @@
       <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="62">
         <v>45444</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="62">
         <v>45473</v>
       </c>
       <c r="F13" s="8">
@@ -4212,10 +4127,10 @@
       <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="62">
         <v>45474</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="62">
         <v>45504</v>
       </c>
       <c r="F14" s="8">
@@ -4229,10 +4144,10 @@
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="62">
         <v>45505</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="62">
         <v>45535</v>
       </c>
       <c r="F15" s="8">
@@ -4243,10 +4158,10 @@
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="5:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="64">
         <f>SUM(F4:F15)</f>
         <v>8484</v>
       </c>
@@ -5919,11 +5834,12 @@
     <col min="38" max="38" width="19.140625" customWidth="1"/>
     <col min="39" max="42" width="6.7109375" style="9" customWidth="1"/>
     <col min="43" max="43" width="9.140625" customWidth="1"/>
-    <col min="44" max="44" width="19.140625" customWidth="1"/>
-    <col min="45" max="45" width="2.7109375" customWidth="1"/>
-    <col min="46" max="49" width="5.7109375" customWidth="1"/>
-    <col min="50" max="50" width="2.7109375" customWidth="1"/>
-    <col min="51" max="55" width="5.7109375" customWidth="1"/>
+    <col min="44" max="44" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="46" max="49" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="51" max="54" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="5.7109375" customWidth="1"/>
     <col min="56" max="56" width="19.140625" customWidth="1"/>
     <col min="57" max="60" width="5.7109375" customWidth="1"/>
     <col min="61" max="64" width="6.7109375" customWidth="1"/>
@@ -5937,94 +5853,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="T1" s="139" t="s">
+      <c r="T1" s="124" t="s">
         <v>129</v>
       </c>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="139"/>
-      <c r="AB1" s="139"/>
-      <c r="AC1" s="139"/>
-      <c r="AD1" s="139"/>
-      <c r="AF1" s="139" t="s">
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="124"/>
+      <c r="AD1" s="124"/>
+      <c r="AF1" s="124" t="s">
         <v>130</v>
       </c>
-      <c r="AG1" s="139"/>
-      <c r="AH1" s="139"/>
-      <c r="AI1" s="139"/>
-      <c r="AJ1" s="139"/>
-      <c r="AK1" s="139"/>
-      <c r="AL1" s="139"/>
-      <c r="AM1" s="139"/>
-      <c r="AN1" s="139"/>
-      <c r="AO1" s="139"/>
-      <c r="AP1" s="139"/>
-      <c r="AQ1" s="139"/>
-      <c r="AR1" s="139"/>
-      <c r="AS1" s="139"/>
-      <c r="AT1" s="139"/>
-      <c r="AU1" s="139"/>
-      <c r="AV1" s="139"/>
-      <c r="AW1" s="139"/>
-      <c r="AX1" s="139"/>
-      <c r="AY1" s="139"/>
-      <c r="AZ1" s="139"/>
-      <c r="BA1" s="139"/>
-      <c r="BB1" s="139"/>
-      <c r="BC1" s="139"/>
-      <c r="BD1" s="139"/>
-      <c r="BE1" s="139"/>
-      <c r="BF1" s="139"/>
-      <c r="BG1" s="139"/>
-      <c r="BH1" s="139"/>
-      <c r="BI1" s="139"/>
-      <c r="BJ1" s="139"/>
-      <c r="BK1" s="139"/>
-      <c r="BL1" s="139"/>
-      <c r="BM1" s="139"/>
-      <c r="BN1" s="139"/>
-      <c r="BO1" s="139"/>
-      <c r="BP1" s="139"/>
-      <c r="BQ1" s="139"/>
-      <c r="BR1" s="139"/>
-      <c r="BS1" s="139"/>
-      <c r="BT1" s="139"/>
-      <c r="BU1" s="139"/>
-      <c r="BV1" s="139"/>
-      <c r="BW1" s="139"/>
-      <c r="BX1" s="139"/>
-      <c r="BY1" s="139"/>
-      <c r="BZ1" s="139"/>
-      <c r="CA1" s="139"/>
-      <c r="CB1" s="139"/>
-      <c r="CC1" s="139"/>
-      <c r="CD1" s="139"/>
-      <c r="CE1" s="139"/>
-      <c r="CF1" s="139"/>
-      <c r="CG1" s="139"/>
-      <c r="CH1" s="139"/>
-      <c r="CI1" s="139"/>
-      <c r="CJ1" s="139"/>
-      <c r="CK1" s="139"/>
-      <c r="CL1" s="139"/>
-      <c r="CM1" s="139"/>
-      <c r="CO1" s="138" t="s">
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="124"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="124"/>
+      <c r="AL1" s="124"/>
+      <c r="AM1" s="124"/>
+      <c r="AN1" s="124"/>
+      <c r="AO1" s="124"/>
+      <c r="AP1" s="124"/>
+      <c r="AQ1" s="124"/>
+      <c r="AR1" s="124"/>
+      <c r="AS1" s="124"/>
+      <c r="AT1" s="124"/>
+      <c r="AU1" s="124"/>
+      <c r="AV1" s="124"/>
+      <c r="AW1" s="124"/>
+      <c r="AX1" s="124"/>
+      <c r="AY1" s="124"/>
+      <c r="AZ1" s="124"/>
+      <c r="BA1" s="124"/>
+      <c r="BB1" s="124"/>
+      <c r="BC1" s="124"/>
+      <c r="BD1" s="124"/>
+      <c r="BE1" s="124"/>
+      <c r="BF1" s="124"/>
+      <c r="BG1" s="124"/>
+      <c r="BH1" s="124"/>
+      <c r="BI1" s="124"/>
+      <c r="BJ1" s="124"/>
+      <c r="BK1" s="124"/>
+      <c r="BL1" s="124"/>
+      <c r="BM1" s="124"/>
+      <c r="BN1" s="124"/>
+      <c r="BO1" s="124"/>
+      <c r="BP1" s="124"/>
+      <c r="BQ1" s="124"/>
+      <c r="BR1" s="124"/>
+      <c r="BS1" s="124"/>
+      <c r="BT1" s="124"/>
+      <c r="BU1" s="124"/>
+      <c r="BV1" s="124"/>
+      <c r="BW1" s="124"/>
+      <c r="BX1" s="124"/>
+      <c r="BY1" s="124"/>
+      <c r="BZ1" s="124"/>
+      <c r="CA1" s="124"/>
+      <c r="CB1" s="124"/>
+      <c r="CC1" s="124"/>
+      <c r="CD1" s="124"/>
+      <c r="CE1" s="124"/>
+      <c r="CF1" s="124"/>
+      <c r="CG1" s="124"/>
+      <c r="CH1" s="124"/>
+      <c r="CI1" s="124"/>
+      <c r="CJ1" s="124"/>
+      <c r="CK1" s="124"/>
+      <c r="CL1" s="124"/>
+      <c r="CM1" s="124"/>
+      <c r="CO1" s="123" t="s">
         <v>131</v>
       </c>
-      <c r="CP1" s="138"/>
-      <c r="CQ1" s="138"/>
-      <c r="CR1" s="138"/>
-      <c r="CS1" s="138"/>
+      <c r="CP1" s="123"/>
+      <c r="CQ1" s="123"/>
+      <c r="CR1" s="123"/>
+      <c r="CS1" s="123"/>
       <c r="CW1" s="52" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>127</v>
       </c>
       <c r="H2" t="s">
@@ -6036,7 +5952,7 @@
       <c r="AF2" t="s">
         <v>54</v>
       </c>
-      <c r="AL2" s="66" t="s">
+      <c r="AL2" s="65" t="s">
         <v>128</v>
       </c>
       <c r="AR2" t="s">
@@ -6065,22 +5981,22 @@
       </c>
     </row>
     <row r="3" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="68" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="26" t="s">
@@ -6116,27 +6032,27 @@
       <c r="R3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="90" t="s">
+      <c r="T3" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="91" t="s">
+      <c r="U3" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="V3" s="91" t="s">
+      <c r="V3" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="W3" s="91" t="s">
+      <c r="W3" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="X3" s="91" t="s">
+      <c r="X3" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="93"/>
+      <c r="Y3" s="91"/>
+      <c r="Z3" s="91"/>
+      <c r="AA3" s="91"/>
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
+      <c r="AD3" s="92"/>
       <c r="AF3" s="27"/>
       <c r="AG3" s="28" t="s">
         <v>64</v>
@@ -6151,7 +6067,7 @@
         <v>67</v>
       </c>
       <c r="AK3" s="30"/>
-      <c r="AL3" s="67" t="s">
+      <c r="AL3" s="66" t="s">
         <v>48</v>
       </c>
       <c r="AM3" s="31" t="s">
@@ -6201,36 +6117,36 @@
       </c>
       <c r="BC3" s="12"/>
       <c r="BD3" s="15"/>
-      <c r="BE3" s="140" t="s">
+      <c r="BE3" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="BF3" s="140"/>
-      <c r="BG3" s="140"/>
-      <c r="BH3" s="140"/>
-      <c r="BI3" s="140" t="s">
+      <c r="BF3" s="125"/>
+      <c r="BG3" s="125"/>
+      <c r="BH3" s="125"/>
+      <c r="BI3" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="BJ3" s="140"/>
-      <c r="BK3" s="140"/>
-      <c r="BL3" s="141"/>
+      <c r="BJ3" s="125"/>
+      <c r="BK3" s="125"/>
+      <c r="BL3" s="126"/>
       <c r="BM3" s="12"/>
       <c r="BN3" s="12"/>
-      <c r="BP3" s="137" t="s">
+      <c r="BP3" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="BQ3" s="137"/>
-      <c r="BR3" s="137" t="s">
+      <c r="BQ3" s="122"/>
+      <c r="BR3" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="137"/>
-      <c r="BT3" s="137" t="s">
+      <c r="BS3" s="122"/>
+      <c r="BT3" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="BU3" s="137"/>
-      <c r="BV3" s="137" t="s">
+      <c r="BU3" s="122"/>
+      <c r="BV3" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="BW3" s="137"/>
+      <c r="BW3" s="122"/>
       <c r="BY3" s="37" t="s">
         <v>74</v>
       </c>
@@ -6253,10 +6169,10 @@
       <c r="CM3" t="s">
         <v>78</v>
       </c>
-      <c r="CP3" s="137" t="s">
+      <c r="CP3" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="CQ3" s="137"/>
+      <c r="CQ3" s="122"/>
       <c r="CR3" t="s">
         <v>80</v>
       </c>
@@ -6271,19 +6187,19 @@
       <c r="A4" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="71">
+      <c r="B4" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="70">
         <v>6</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="70">
         <v>32</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="70">
         <v>2</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="71">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
@@ -6319,33 +6235,33 @@
       <c r="R4" s="23">
         <v>0</v>
       </c>
-      <c r="T4" s="94" t="s">
+      <c r="T4" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="95">
+      <c r="U4" s="94">
         <v>2</v>
       </c>
-      <c r="V4" s="95">
+      <c r="V4" s="94">
         <v>14</v>
       </c>
-      <c r="W4" s="95">
-        <v>0</v>
-      </c>
-      <c r="X4" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="96"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96" t="s">
+      <c r="W4" s="94">
+        <v>0</v>
+      </c>
+      <c r="X4" s="94">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="95"/>
+      <c r="Z4" s="95"/>
+      <c r="AA4" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB4" s="96" t="s">
+      <c r="AB4" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="AC4" s="96" t="s">
+      <c r="AC4" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="AD4" s="97" t="s">
+      <c r="AD4" s="96" t="s">
         <v>90</v>
       </c>
       <c r="AF4" s="40" t="s">
@@ -6370,19 +6286,19 @@
       <c r="AL4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="77">
+      <c r="AM4" s="76">
         <f t="shared" ref="AM4:AM35" si="0">(AG$4-C4)/(AG$4-AG$5)</f>
         <v>0.98070739549839225</v>
       </c>
-      <c r="AN4" s="78">
+      <c r="AN4" s="77">
         <f t="shared" ref="AN4:AN35" si="1">(D4-AH$5)/(AH$4-AH$5)</f>
         <v>0.1807909604519774</v>
       </c>
-      <c r="AO4" s="78">
+      <c r="AO4" s="77">
         <f t="shared" ref="AO4:AO35" si="2">(E4-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP4" s="79">
+      <c r="AP4" s="78">
         <f t="shared" ref="AP4:AP35" si="3">(AJ$4-F4)/(AJ$4-AJ$5)</f>
         <v>1</v>
       </c>
@@ -6448,37 +6364,37 @@
       <c r="BM4" s="45"/>
       <c r="BN4" s="45"/>
       <c r="BO4" s="30"/>
-      <c r="BP4" s="117">
+      <c r="BP4" s="115">
         <f>AA37</f>
-        <v>0</v>
-      </c>
-      <c r="BQ4" s="118">
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="BQ4" s="116">
         <f>AA38</f>
-        <v>0.20227272727272727</v>
-      </c>
-      <c r="BR4" s="118">
+        <v>7.3333333333333334E-2</v>
+      </c>
+      <c r="BR4" s="116">
         <f>AA39</f>
-        <v>1.3636363636363627E-2</v>
-      </c>
-      <c r="BS4" s="118">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="BS4" s="116">
         <f>AA40</f>
-        <v>0.41818181818181821</v>
-      </c>
-      <c r="BT4" s="118">
+        <v>0.22814814814814816</v>
+      </c>
+      <c r="BT4" s="116">
         <f>AB37</f>
-        <v>0.29772727272727273</v>
-      </c>
-      <c r="BU4" s="118">
+        <v>0.36206896551724138</v>
+      </c>
+      <c r="BU4" s="116">
         <f>AB38</f>
-        <v>0.64545454545454539</v>
-      </c>
-      <c r="BV4" s="118">
+        <v>0.60689655172413792</v>
+      </c>
+      <c r="BV4" s="116">
         <f>AB39</f>
-        <v>0.12727272727272726</v>
-      </c>
-      <c r="BW4" s="119">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="BW4" s="117">
         <f>AB40</f>
-        <v>0.47499999999999998</v>
+        <v>0.41724137931034483</v>
       </c>
       <c r="BY4" s="37" t="s">
         <v>91</v>
@@ -6487,46 +6403,46 @@
       <c r="CA4" s="2"/>
       <c r="CB4" s="2"/>
       <c r="CC4" s="2"/>
-      <c r="CI4" s="120" t="s">
-        <v>1</v>
-      </c>
-      <c r="CJ4" s="121">
-        <f t="shared" ref="CJ4:CJ19" si="4">(BZ6+CD6+BZ23+CD23)/$T$41</f>
-        <v>2.3279906364154754E-2</v>
-      </c>
-      <c r="CK4" s="122">
-        <f t="shared" ref="CK4:CK19" si="5">(CA6+CE6+CA23+CE23)/$T$41</f>
-        <v>0.34177212849126987</v>
-      </c>
-      <c r="CL4" s="122">
-        <f t="shared" ref="CL4:CL19" si="6">(CB6+CF6+CB23+CF23)/$T$41</f>
-        <v>2.2348634165063556E-2</v>
-      </c>
-      <c r="CM4" s="123">
-        <f t="shared" ref="CM4:CM19" si="7">(CC6+CG6+CC23+CG23)/$T$41</f>
-        <v>0.38459378713378833</v>
-      </c>
-      <c r="CO4" s="120" t="s">
-        <v>1</v>
-      </c>
-      <c r="CP4" s="121">
-        <f t="shared" ref="CP4:CP19" si="8">CJ4-CM4</f>
-        <v>-0.36131388076963356</v>
-      </c>
-      <c r="CQ4" s="122">
-        <f t="shared" ref="CQ4:CQ19" si="9">CK4-CL4</f>
-        <v>0.31942349432620631</v>
-      </c>
-      <c r="CR4" s="129">
-        <f t="shared" ref="CR4:CS19" si="10">(CP4+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>8.3172790190607054E-2</v>
-      </c>
-      <c r="CS4" s="130">
-        <f t="shared" si="10"/>
-        <v>0.78296409412688073</v>
+      <c r="CI4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ4" s="14">
+        <f t="shared" ref="CJ4:CM11" si="4">(BZ6+CD6+BZ23+CD23)/$T$41</f>
+        <v>3.0098860552148211E-2</v>
+      </c>
+      <c r="CK4" s="14">
+        <f t="shared" si="4"/>
+        <v>0.25544601952503931</v>
+      </c>
+      <c r="CL4" s="14">
+        <f t="shared" si="4"/>
+        <v>6.0302151241232518E-2</v>
+      </c>
+      <c r="CM4" s="14">
+        <f t="shared" si="4"/>
+        <v>0.30167184371666395</v>
+      </c>
+      <c r="CO4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CP4" s="14">
+        <f t="shared" ref="CP4:CP19" si="5">CJ4-CM4</f>
+        <v>-0.27157298316451572</v>
+      </c>
+      <c r="CQ4" s="14">
+        <f t="shared" ref="CQ4:CQ19" si="6">CK4-CL4</f>
+        <v>0.19514386828380681</v>
+      </c>
+      <c r="CR4" s="49">
+        <f t="shared" ref="CR4:CS19" si="7">(CP4+$CP$21)/($CP$21+$CQ$21)</f>
+        <v>9.0087567627719273E-2</v>
+      </c>
+      <c r="CS4" s="49">
+        <f t="shared" si="7"/>
+        <v>0.71222889661843003</v>
       </c>
       <c r="CU4" s="14"/>
-      <c r="CW4" s="134">
+      <c r="CW4" s="118">
         <f>RANK(CR4,$CR$4:$CR$19,0)</f>
         <v>8</v>
       </c>
@@ -6584,33 +6500,33 @@
       <c r="R5" s="23">
         <v>0</v>
       </c>
-      <c r="T5" s="94" t="s">
+      <c r="T5" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="U5" s="95">
+      <c r="U5" s="94">
         <v>3</v>
       </c>
-      <c r="V5" s="95">
+      <c r="V5" s="94">
         <v>31</v>
       </c>
-      <c r="W5" s="95">
-        <v>0</v>
-      </c>
-      <c r="X5" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96" t="s">
+      <c r="W5" s="94">
+        <v>0</v>
+      </c>
+      <c r="X5" s="94">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="AB5" s="96" t="s">
+      <c r="AB5" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="AC5" s="98" t="s">
+      <c r="AC5" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="AD5" s="97" t="s">
+      <c r="AD5" s="96" t="s">
         <v>96</v>
       </c>
       <c r="AF5" s="40" t="s">
@@ -6647,7 +6563,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP5" s="80">
+      <c r="AP5" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6693,15 +6609,15 @@
         <v>0.53697749196141475</v>
       </c>
       <c r="BF5" s="13">
-        <f t="shared" ref="BF5:BH20" si="11">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BF5:BH20" si="8">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.1807909604519774</v>
       </c>
       <c r="BG5" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH5" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI5" s="13">
@@ -6709,36 +6625,36 @@
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ5" s="13">
-        <f t="shared" ref="BJ5:BL20" si="12">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BJ5:BL20" si="9">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.60451977401129942</v>
       </c>
       <c r="BK5" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.23076923076923078</v>
       </c>
       <c r="BL5" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM5" s="45"/>
       <c r="BN5" s="45"/>
       <c r="BO5" s="30"/>
-      <c r="BP5" s="142" t="s">
+      <c r="BP5" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="BQ5" s="143"/>
-      <c r="BR5" s="142" t="s">
+      <c r="BQ5" s="128"/>
+      <c r="BR5" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="BS5" s="143"/>
-      <c r="BT5" s="142" t="s">
+      <c r="BS5" s="128"/>
+      <c r="BT5" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="BU5" s="143"/>
-      <c r="BV5" s="142" t="s">
+      <c r="BU5" s="128"/>
+      <c r="BV5" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="BW5" s="143"/>
+      <c r="BW5" s="128"/>
       <c r="BY5" s="38"/>
       <c r="BZ5" s="51" t="s">
         <v>97</v>
@@ -6764,47 +6680,47 @@
       <c r="CG5" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="CI5" s="120" t="s">
+      <c r="CI5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="CJ5" s="124">
+      <c r="CJ5" s="14">
         <f t="shared" si="4"/>
-        <v>1.6956374066953075E-2</v>
+        <v>2.6369491717315605E-2</v>
       </c>
       <c r="CK5" s="14">
+        <f t="shared" si="4"/>
+        <v>0.42174398908604505</v>
+      </c>
+      <c r="CL5" s="14">
+        <f t="shared" si="4"/>
+        <v>1.0720517487761429E-2</v>
+      </c>
+      <c r="CM5" s="14">
+        <f t="shared" si="4"/>
+        <v>0.18384331469360701</v>
+      </c>
+      <c r="CO5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="CP5" s="14">
         <f t="shared" si="5"/>
-        <v>0.53724924866961732</v>
-      </c>
-      <c r="CL5" s="14">
+        <v>-0.15747382297629142</v>
+      </c>
+      <c r="CQ5" s="14">
         <f t="shared" si="6"/>
-        <v>6.6993055942432345E-3</v>
-      </c>
-      <c r="CM5" s="125">
+        <v>0.41102347159828362</v>
+      </c>
+      <c r="CR5" s="49">
         <f t="shared" si="7"/>
-        <v>0.2201099911950217</v>
-      </c>
-      <c r="CO5" s="120" t="s">
-        <v>2</v>
-      </c>
-      <c r="CP5" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.20315361712806862</v>
-      </c>
-      <c r="CQ5" s="14">
-        <f t="shared" si="9"/>
-        <v>0.53054994307537406</v>
-      </c>
-      <c r="CR5" s="49">
-        <f t="shared" si="10"/>
-        <v>0.24575998045477201</v>
-      </c>
-      <c r="CS5" s="131">
-        <f t="shared" si="10"/>
+        <v>0.24218364672994513</v>
+      </c>
+      <c r="CS5" s="49">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="CU5" s="14"/>
-      <c r="CW5" s="135">
-        <f t="shared" ref="CW5:CW19" si="13">RANK(CR5,$CR$4:$CR$19,0)</f>
+      <c r="CW5" s="119">
+        <f t="shared" ref="CW5:CW19" si="10">RANK(CR5,$CR$4:$CR$19,0)</f>
         <v>1</v>
       </c>
       <c r="CY5" s="14"/>
@@ -6861,33 +6777,33 @@
       <c r="R6" s="23">
         <v>1</v>
       </c>
-      <c r="T6" s="94" t="s">
+      <c r="T6" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="95">
+      <c r="U6" s="94">
         <v>4</v>
       </c>
-      <c r="V6" s="95">
+      <c r="V6" s="94">
         <v>31</v>
       </c>
-      <c r="W6" s="95">
-        <v>1</v>
-      </c>
-      <c r="X6" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="96"/>
-      <c r="Z6" s="96"/>
-      <c r="AA6" s="96" t="s">
+      <c r="W6" s="94">
+        <v>1</v>
+      </c>
+      <c r="X6" s="94">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="95"/>
+      <c r="AA6" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="AB6" s="96" t="s">
+      <c r="AB6" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="AC6" s="96" t="s">
+      <c r="AC6" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="AD6" s="97" t="s">
+      <c r="AD6" s="96" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="17"/>
@@ -6918,7 +6834,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="80">
+      <c r="AP6" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6960,35 +6876,35 @@
         <v>2</v>
       </c>
       <c r="BE6" s="13">
-        <f t="shared" ref="BE6:BE20" si="14">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BE6:BE20" si="11">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>0.99356913183279738</v>
       </c>
       <c r="BF6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BH6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="BI6" s="13">
-        <f t="shared" ref="BI6:BI20" si="15">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BI6:BI20" si="12">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>1</v>
       </c>
       <c r="BJ6" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.81355932203389836</v>
       </c>
       <c r="BK6" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BL6" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM6" s="45"/>
@@ -7023,78 +6939,78 @@
       </c>
       <c r="BZ6" s="13">
         <f>BP7*BP$4</f>
-        <v>0</v>
+        <v>4.9371766444937203E-3</v>
       </c>
       <c r="CA6" s="13">
-        <f t="shared" ref="CA6:CG21" si="16">BQ7*BQ$4</f>
-        <v>0.13768897399717797</v>
+        <f t="shared" ref="CA6:CG21" si="13">BQ7*BQ$4</f>
+        <v>4.991869918699187E-2</v>
       </c>
       <c r="CB6" s="13">
-        <f t="shared" si="16"/>
-        <v>1.2094335819391225E-4</v>
+        <f t="shared" si="13"/>
+        <v>5.9127864005912689E-4</v>
       </c>
       <c r="CC6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.13352146744607943</v>
+        <f t="shared" si="13"/>
+        <v>7.2845528455284553E-2</v>
       </c>
       <c r="CD6" s="13">
-        <f t="shared" si="16"/>
-        <v>3.7806637806637816E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.597701149425288E-2</v>
       </c>
       <c r="CE6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.27406204906204906</v>
+        <f t="shared" si="13"/>
+        <v>0.25769020251778874</v>
       </c>
       <c r="CF6" s="13">
-        <f t="shared" si="16"/>
-        <v>3.5353535353535359E-2</v>
+        <f t="shared" si="13"/>
+        <v>5.7471264367816105E-2</v>
       </c>
       <c r="CG6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.27331349206349209</v>
-      </c>
-      <c r="CI6" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.24007936507936511</v>
+      </c>
+      <c r="CI6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="CJ6" s="124">
+      <c r="CJ6" s="14">
         <f t="shared" si="4"/>
-        <v>5.916420923992455E-3</v>
+        <v>1.0982519810541774E-2</v>
       </c>
       <c r="CK6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.12565480085429181</v>
+      </c>
+      <c r="CL6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.12306487006224393</v>
+      </c>
+      <c r="CM6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.35013723072501501</v>
+      </c>
+      <c r="CO6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CP6" s="14">
         <f t="shared" si="5"/>
-        <v>0.21422228179620384</v>
-      </c>
-      <c r="CL6" s="14">
+        <v>-0.33915471091447325</v>
+      </c>
+      <c r="CQ6" s="14">
         <f t="shared" si="6"/>
-        <v>5.6161128529025231E-2</v>
-      </c>
-      <c r="CM6" s="125">
+        <v>2.5899307920478898E-3</v>
+      </c>
+      <c r="CR6" s="49">
         <f t="shared" si="7"/>
-        <v>0.43428820621476238</v>
-      </c>
-      <c r="CO6" s="120" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP6" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.42837178529076991</v>
-      </c>
-      <c r="CQ6" s="14">
-        <f t="shared" si="9"/>
-        <v>0.15806115326717862</v>
-      </c>
-      <c r="CR6" s="49">
+        <v>0</v>
+      </c>
+      <c r="CS6" s="49">
+        <f t="shared" si="7"/>
+        <v>0.45555129390971016</v>
+      </c>
+      <c r="CU6" s="14"/>
+      <c r="CW6" s="119">
         <f t="shared" si="10"/>
-        <v>1.4237926084646286E-2</v>
-      </c>
-      <c r="CS6" s="131">
-        <f t="shared" si="10"/>
-        <v>0.61708519987635002</v>
-      </c>
-      <c r="CU6" s="14"/>
-      <c r="CW6" s="135">
-        <f t="shared" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CY6" s="14"/>
     </row>
@@ -7150,27 +7066,27 @@
       <c r="R7" s="23">
         <v>0</v>
       </c>
-      <c r="T7" s="94" t="s">
+      <c r="T7" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="U7" s="95">
+      <c r="U7" s="94">
         <v>5</v>
       </c>
-      <c r="V7" s="95">
+      <c r="V7" s="94">
         <v>33</v>
       </c>
-      <c r="W7" s="95">
-        <v>1</v>
-      </c>
-      <c r="X7" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="96"/>
-      <c r="AB7" s="96"/>
-      <c r="AC7" s="96"/>
-      <c r="AD7" s="97"/>
+      <c r="W7" s="94">
+        <v>1</v>
+      </c>
+      <c r="X7" s="94">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="95"/>
+      <c r="Z7" s="95"/>
+      <c r="AA7" s="95"/>
+      <c r="AB7" s="95"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="96"/>
       <c r="AL7" s="39" t="s">
         <v>5</v>
       </c>
@@ -7186,7 +7102,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="80">
+      <c r="AP7" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -7228,35 +7144,35 @@
         <v>4</v>
       </c>
       <c r="BE7" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="BF7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>4.519774011299435E-2</v>
       </c>
       <c r="BG7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI7" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.95176848874598075</v>
       </c>
       <c r="BJ7" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="BK7" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL7" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM7" s="45"/>
@@ -7292,78 +7208,78 @@
         <v>2</v>
       </c>
       <c r="BZ7" s="13">
-        <f t="shared" ref="BZ7:BZ21" si="17">BP8*BP$4</f>
-        <v>0</v>
+        <f t="shared" ref="BZ7:BZ21" si="14">BP8*BP$4</f>
+        <v>1.3162939297124603E-2</v>
       </c>
       <c r="CA7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.20098024978216672</v>
+        <f t="shared" si="13"/>
+        <v>7.2864749733759324E-2</v>
       </c>
       <c r="CB7" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CC7" s="13">
-        <f t="shared" si="16"/>
-        <v>2.6720882950915098E-3</v>
+        <f t="shared" si="13"/>
+        <v>1.4578156431191683E-3</v>
       </c>
       <c r="CD7" s="13">
-        <f t="shared" si="16"/>
-        <v>2.1906354515050169E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.6640525890900706E-2</v>
       </c>
       <c r="CE7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.31085436302827607</v>
+        <f t="shared" si="13"/>
+        <v>0.29228462691731055</v>
       </c>
       <c r="CF7" s="13">
-        <f t="shared" si="16"/>
-        <v>1.404682274247491E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.2834736477914883E-2</v>
       </c>
       <c r="CG7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.24623745819397991</v>
-      </c>
-      <c r="CI7" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.21629569830469381</v>
+      </c>
+      <c r="CI7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="CJ7" s="124">
+      <c r="CJ7" s="14">
         <f t="shared" si="4"/>
-        <v>1.4199410217581893E-2</v>
+        <v>2.2098390184489201E-2</v>
       </c>
       <c r="CK7" s="14">
+        <f t="shared" si="4"/>
+        <v>0.19854653895579252</v>
+      </c>
+      <c r="CL7" s="14">
+        <f t="shared" si="4"/>
+        <v>8.0785368368311974E-2</v>
+      </c>
+      <c r="CM7" s="14">
+        <f t="shared" si="4"/>
+        <v>0.29096603101747631</v>
+      </c>
+      <c r="CO7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP7" s="14">
         <f t="shared" si="5"/>
-        <v>0.29940862357535669</v>
-      </c>
-      <c r="CL7" s="14">
+        <v>-0.26886764083298709</v>
+      </c>
+      <c r="CQ7" s="14">
         <f t="shared" si="6"/>
-        <v>3.007207186692322E-2</v>
-      </c>
-      <c r="CM7" s="125">
+        <v>0.11776117058748055</v>
+      </c>
+      <c r="CR7" s="49">
         <f t="shared" si="7"/>
-        <v>0.35765434347804642</v>
-      </c>
-      <c r="CO7" s="120" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP7" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.3434549332604645</v>
-      </c>
-      <c r="CQ7" s="14">
-        <f t="shared" si="9"/>
-        <v>0.26933655170843346</v>
-      </c>
-      <c r="CR7" s="49">
+        <v>9.3693833971625687E-2</v>
+      </c>
+      <c r="CS7" s="49">
+        <f t="shared" si="7"/>
+        <v>0.60907647296738576</v>
+      </c>
+      <c r="CU7" s="14"/>
+      <c r="CW7" s="119">
         <f t="shared" si="10"/>
-        <v>0.10153161199411295</v>
-      </c>
-      <c r="CS7" s="131">
-        <f t="shared" si="10"/>
-        <v>0.73147521138449001</v>
-      </c>
-      <c r="CU7" s="14"/>
-      <c r="CW7" s="135">
-        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="CY7" s="14"/>
@@ -7420,25 +7336,25 @@
       <c r="R8" s="23">
         <v>2</v>
       </c>
-      <c r="T8" s="94"/>
-      <c r="U8" s="95">
+      <c r="T8" s="93"/>
+      <c r="U8" s="94">
         <v>9</v>
       </c>
-      <c r="V8" s="95">
+      <c r="V8" s="94">
         <v>38</v>
       </c>
-      <c r="W8" s="95">
-        <v>1</v>
-      </c>
-      <c r="X8" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="97"/>
+      <c r="W8" s="94">
+        <v>1</v>
+      </c>
+      <c r="X8" s="94">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="96"/>
       <c r="AL8" s="39" t="s">
         <v>6</v>
       </c>
@@ -7454,7 +7370,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP8" s="80">
+      <c r="AP8" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7496,35 +7412,35 @@
         <v>5</v>
       </c>
       <c r="BE8" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="BF8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.13559322033898305</v>
       </c>
       <c r="BG8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.98392282958199362</v>
       </c>
       <c r="BJ8" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="BK8" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL8" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM8" s="45"/>
@@ -7560,78 +7476,78 @@
         <v>4</v>
       </c>
       <c r="BZ8" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>8.3065953654188947E-3</v>
       </c>
       <c r="CA8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.16008750607681091</v>
+        <f t="shared" si="13"/>
+        <v>5.8039215686274515E-2</v>
       </c>
       <c r="CB8" s="13">
-        <f t="shared" si="16"/>
-        <v>5.4691298006805946E-4</v>
+        <f t="shared" si="13"/>
+        <v>2.6737967914438479E-3</v>
       </c>
       <c r="CC8" s="13">
-        <f t="shared" si="16"/>
-        <v>8.7214389888186708E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.7581699346405243E-2</v>
       </c>
       <c r="CD8" s="13">
-        <f t="shared" si="16"/>
-        <v>1.240530303030303E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.5086206896551723E-2</v>
       </c>
       <c r="CE8" s="13">
-        <f t="shared" si="16"/>
-        <v>7.732007575757574E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.2701149425287354E-2</v>
       </c>
       <c r="CF8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.10208333333333332</v>
+        <f t="shared" si="13"/>
+        <v>0.16594827586206895</v>
       </c>
       <c r="CG8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.41809895833333327</v>
-      </c>
-      <c r="CI8" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.36725933908045977</v>
+      </c>
+      <c r="CI8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="CJ8" s="124">
+      <c r="CJ8" s="14">
         <f t="shared" si="4"/>
-        <v>4.0221505337356425E-2</v>
+        <v>5.2719220784385887E-2</v>
       </c>
       <c r="CK8" s="14">
+        <f t="shared" si="4"/>
+        <v>0.25528185753442001</v>
+      </c>
+      <c r="CL8" s="14">
+        <f t="shared" si="4"/>
+        <v>6.5347336609976367E-2</v>
+      </c>
+      <c r="CM8" s="14">
+        <f t="shared" si="4"/>
+        <v>0.26223178088694649</v>
+      </c>
+      <c r="CO8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP8" s="14">
         <f t="shared" si="5"/>
-        <v>0.35605324925446225</v>
-      </c>
-      <c r="CL8" s="14">
+        <v>-0.20951256010256059</v>
+      </c>
+      <c r="CQ8" s="14">
         <f t="shared" si="6"/>
-        <v>2.1377078452592617E-2</v>
-      </c>
-      <c r="CM8" s="125">
+        <v>0.18993452092444363</v>
+      </c>
+      <c r="CR8" s="49">
         <f t="shared" si="7"/>
-        <v>0.32876028498786058</v>
-      </c>
-      <c r="CO8" s="120" t="s">
-        <v>6</v>
-      </c>
-      <c r="CP8" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.28853877965050417</v>
-      </c>
-      <c r="CQ8" s="14">
-        <f t="shared" si="9"/>
-        <v>0.33467617080186962</v>
-      </c>
-      <c r="CR8" s="49">
+        <v>0.17281514423369421</v>
+      </c>
+      <c r="CS8" s="49">
+        <f t="shared" si="7"/>
+        <v>0.70528474990662582</v>
+      </c>
+      <c r="CU8" s="14"/>
+      <c r="CW8" s="119">
         <f t="shared" si="10"/>
-        <v>0.15798487598078384</v>
-      </c>
-      <c r="CS8" s="131">
-        <f t="shared" si="10"/>
-        <v>0.79864369502718369</v>
-      </c>
-      <c r="CU8" s="14"/>
-      <c r="CW8" s="135">
-        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="CY8" s="14"/>
@@ -7688,25 +7604,25 @@
       <c r="R9" s="23">
         <v>2</v>
       </c>
-      <c r="T9" s="94"/>
-      <c r="U9" s="95">
+      <c r="T9" s="93"/>
+      <c r="U9" s="94">
         <v>10</v>
       </c>
-      <c r="V9" s="95">
+      <c r="V9" s="94">
         <v>40</v>
       </c>
-      <c r="W9" s="95">
-        <v>1</v>
-      </c>
-      <c r="X9" s="95">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="96"/>
-      <c r="AD9" s="97"/>
+      <c r="W9" s="94">
+        <v>1</v>
+      </c>
+      <c r="X9" s="94">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="95"/>
+      <c r="Z9" s="95"/>
+      <c r="AA9" s="95"/>
+      <c r="AB9" s="95"/>
+      <c r="AC9" s="95"/>
+      <c r="AD9" s="96"/>
       <c r="AL9" s="39" t="s">
         <v>8</v>
       </c>
@@ -7722,7 +7638,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP9" s="80">
+      <c r="AP9" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7764,35 +7680,35 @@
         <v>6</v>
       </c>
       <c r="BE9" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.81672025723472674</v>
       </c>
       <c r="BF9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ9" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.68926553672316382</v>
       </c>
       <c r="BK9" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL9" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM9" s="45"/>
@@ -7828,78 +7744,78 @@
         <v>5</v>
       </c>
       <c r="BZ9" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.0862745098039216E-2</v>
       </c>
       <c r="CA9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.18204545454545457</v>
+        <f t="shared" si="13"/>
+        <v>6.6000000000000017E-2</v>
       </c>
       <c r="CB9" s="13">
-        <f t="shared" si="16"/>
-        <v>2.0053475935828802E-4</v>
+        <f t="shared" si="13"/>
+        <v>9.8039215686274205E-4</v>
       </c>
       <c r="CC9" s="13">
-        <f t="shared" si="16"/>
-        <v>4.1818181818181831E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.2814814814814819E-2</v>
       </c>
       <c r="CD9" s="13">
-        <f t="shared" si="16"/>
-        <v>2.9772727272727274E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.6206896551724141E-2</v>
       </c>
       <c r="CE9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.23397727272727273</v>
+        <f t="shared" si="13"/>
+        <v>0.22000000000000003</v>
       </c>
       <c r="CF9" s="13">
-        <f t="shared" si="16"/>
-        <v>4.7727272727272722E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.7586206896551727E-2</v>
       </c>
       <c r="CG9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.30281250000000004</v>
-      </c>
-      <c r="CI9" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.26599137931034483</v>
+      </c>
+      <c r="CI9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="CJ9" s="124">
+      <c r="CJ9" s="14">
         <f t="shared" si="4"/>
-        <v>2.2746628018456429E-2</v>
+        <v>3.2271689776760537E-2</v>
       </c>
       <c r="CK9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.17766453417780589</v>
+      </c>
+      <c r="CL9" s="14">
+        <f t="shared" si="4"/>
+        <v>9.9048473133388867E-2</v>
+      </c>
+      <c r="CM9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.31898561877005455</v>
+      </c>
+      <c r="CO9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP9" s="14">
         <f t="shared" si="5"/>
-        <v>0.27333951118717009</v>
-      </c>
-      <c r="CL9" s="14">
+        <v>-0.28671392899329401</v>
+      </c>
+      <c r="CQ9" s="14">
         <f t="shared" si="6"/>
-        <v>4.1291656483939801E-2</v>
-      </c>
-      <c r="CM9" s="125">
+        <v>7.8616061044417027E-2</v>
+      </c>
+      <c r="CR9" s="49">
         <f t="shared" si="7"/>
-        <v>0.39080612502732326</v>
-      </c>
-      <c r="CO9" s="120" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP9" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.36805949700886681</v>
-      </c>
-      <c r="CQ9" s="14">
-        <f t="shared" si="9"/>
-        <v>0.23204785470323031</v>
-      </c>
-      <c r="CR9" s="49">
+        <v>6.9904434897755066E-2</v>
+      </c>
+      <c r="CS9" s="49">
+        <f t="shared" si="7"/>
+        <v>0.55689539058513748</v>
+      </c>
+      <c r="CU9" s="14"/>
+      <c r="CW9" s="119">
         <f t="shared" si="10"/>
-        <v>7.6238363263861408E-2</v>
-      </c>
-      <c r="CS9" s="131">
-        <f t="shared" si="10"/>
-        <v>0.6931427988359915</v>
-      </c>
-      <c r="CU9" s="14"/>
-      <c r="CW9" s="135">
-        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="CY9" s="14"/>
@@ -7956,25 +7872,25 @@
       <c r="R10" s="23">
         <v>2</v>
       </c>
-      <c r="T10" s="94"/>
-      <c r="U10" s="95">
+      <c r="T10" s="93"/>
+      <c r="U10" s="94">
         <v>12</v>
       </c>
-      <c r="V10" s="95">
+      <c r="V10" s="94">
         <v>52</v>
       </c>
-      <c r="W10" s="95">
-        <v>1</v>
-      </c>
-      <c r="X10" s="95">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="97"/>
+      <c r="W10" s="94">
+        <v>1</v>
+      </c>
+      <c r="X10" s="94">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="95"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="95"/>
+      <c r="AB10" s="95"/>
+      <c r="AC10" s="95"/>
+      <c r="AD10" s="96"/>
       <c r="AL10" s="39" t="s">
         <v>9</v>
       </c>
@@ -7990,7 +7906,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP10" s="80">
+      <c r="AP10" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -8032,35 +7948,35 @@
         <v>8</v>
       </c>
       <c r="BE10" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BF10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="BG10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI10" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BJ10" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.35028248587570621</v>
       </c>
       <c r="BK10" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL10" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM10" s="45"/>
@@ -8096,79 +8012,79 @@
         <v>6</v>
       </c>
       <c r="BZ10" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>9.7318007662835267E-3</v>
       </c>
       <c r="CA10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.16914184952978056</v>
+        <f t="shared" si="13"/>
+        <v>6.1321839080459774E-2</v>
       </c>
       <c r="CB10" s="13">
-        <f t="shared" si="16"/>
-        <v>7.8369905956112839E-4</v>
+        <f t="shared" si="13"/>
+        <v>3.8314176245210743E-3</v>
       </c>
       <c r="CC10" s="13">
-        <f t="shared" si="16"/>
-        <v>6.8495297805642619E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.7369093231162193E-2</v>
       </c>
       <c r="CD10" s="13">
-        <f t="shared" si="16"/>
-        <v>8.4334763948497843E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.10256030782891815</v>
       </c>
       <c r="CE10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.33796332422941855</v>
+        <f t="shared" si="13"/>
+        <v>0.31777416013023524</v>
       </c>
       <c r="CF10" s="13">
-        <f t="shared" si="16"/>
-        <v>3.0042918454935619E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.8838241823294361E-2</v>
       </c>
       <c r="CG10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.22628755364806863</v>
-      </c>
-      <c r="CI10" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.19877164422080801</v>
+      </c>
+      <c r="CI10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="CJ10" s="124">
+      <c r="CJ10" s="14">
         <f t="shared" si="4"/>
-        <v>1.0789825393299311E-2</v>
+        <v>1.5915960045062537E-2</v>
       </c>
       <c r="CK10" s="14">
+        <f t="shared" si="4"/>
+        <v>0.24151494016239741</v>
+      </c>
+      <c r="CL10" s="14">
+        <f t="shared" si="4"/>
+        <v>4.215786143094246E-2</v>
+      </c>
+      <c r="CM10" s="14">
+        <f t="shared" si="4"/>
+        <v>0.34086343511727729</v>
+      </c>
+      <c r="CO10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="CP10" s="14">
         <f t="shared" si="5"/>
-        <v>0.3209679558890487</v>
-      </c>
-      <c r="CL10" s="14">
+        <v>-0.32494747507221478</v>
+      </c>
+      <c r="CQ10" s="14">
         <f t="shared" si="6"/>
-        <v>6.9946243841363673E-3</v>
-      </c>
-      <c r="CM10" s="125">
+        <v>0.19935707873145495</v>
+      </c>
+      <c r="CR10" s="49">
         <f t="shared" si="7"/>
-        <v>0.42808072583239892</v>
-      </c>
-      <c r="CO10" s="120" t="s">
-        <v>9</v>
-      </c>
-      <c r="CP10" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.41729090043909961</v>
-      </c>
-      <c r="CQ10" s="14">
-        <f t="shared" si="9"/>
-        <v>0.3139733315049123</v>
-      </c>
-      <c r="CR10" s="49">
+        <v>1.8938481781315832E-2</v>
+      </c>
+      <c r="CS10" s="49">
+        <f t="shared" si="7"/>
+        <v>0.71784517625153765</v>
+      </c>
+      <c r="CU10" s="14"/>
+      <c r="CW10" s="119">
         <f t="shared" si="10"/>
-        <v>2.5628966363617819E-2</v>
-      </c>
-      <c r="CS10" s="131">
-        <f t="shared" si="10"/>
-        <v>0.77736138052996484</v>
-      </c>
-      <c r="CU10" s="14"/>
-      <c r="CW10" s="135">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CY10" s="14"/>
     </row>
@@ -8224,25 +8140,25 @@
       <c r="R11" s="23">
         <v>2</v>
       </c>
-      <c r="T11" s="94"/>
-      <c r="U11" s="95">
+      <c r="T11" s="93"/>
+      <c r="U11" s="94">
         <v>20</v>
       </c>
-      <c r="V11" s="95">
+      <c r="V11" s="94">
         <v>54</v>
       </c>
-      <c r="W11" s="95">
-        <v>1</v>
-      </c>
-      <c r="X11" s="95">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="97"/>
+      <c r="W11" s="94">
+        <v>1</v>
+      </c>
+      <c r="X11" s="94">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="95"/>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="95"/>
+      <c r="AB11" s="95"/>
+      <c r="AC11" s="95"/>
+      <c r="AD11" s="96"/>
       <c r="AL11" s="39" t="s">
         <v>10</v>
       </c>
@@ -8258,7 +8174,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP11" s="80">
+      <c r="AP11" s="79">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8300,35 +8216,35 @@
         <v>9</v>
       </c>
       <c r="BE11" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="BF11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.14124293785310735</v>
       </c>
       <c r="BG11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BI11" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ11" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BK11" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL11" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM11" s="45"/>
@@ -8364,78 +8280,78 @@
         <v>8</v>
       </c>
       <c r="BZ11" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.073746312684366E-2</v>
       </c>
       <c r="CA11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.17959908822740681</v>
+        <f t="shared" si="13"/>
+        <v>6.5113077679449363E-2</v>
       </c>
       <c r="CB11" s="13">
-        <f t="shared" si="16"/>
-        <v>4.0225261464199504E-4</v>
+        <f t="shared" si="13"/>
+        <v>1.9665683382497547E-3</v>
       </c>
       <c r="CC11" s="13">
-        <f t="shared" si="16"/>
-        <v>4.6875838026280509E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.5574128700972358E-2</v>
       </c>
       <c r="CD11" s="13">
-        <f t="shared" si="16"/>
-        <v>4.7694174757281549E-2</v>
+        <f t="shared" si="13"/>
+        <v>5.8001339136257109E-2</v>
       </c>
       <c r="CE11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.19426301853486316</v>
+        <f t="shared" si="13"/>
+        <v>0.1826581854703716</v>
       </c>
       <c r="CF11" s="13">
-        <f t="shared" si="16"/>
-        <v>7.1050308914386573E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.11550050217609641</v>
       </c>
       <c r="CG11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.33203883495145625</v>
-      </c>
-      <c r="CI11" s="120" t="s">
+        <f t="shared" si="13"/>
+        <v>0.29166387679946432</v>
+      </c>
+      <c r="CI11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="CJ11" s="124">
+      <c r="CJ11" s="14">
         <f t="shared" si="4"/>
-        <v>2.5770120285137331E-2</v>
+        <v>3.3297804472045639E-2</v>
       </c>
       <c r="CK11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.23207264624358043</v>
+      </c>
+      <c r="CL11" s="14">
+        <f t="shared" si="4"/>
+        <v>9.7199242270108968E-2</v>
+      </c>
+      <c r="CM11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.37003847254276945</v>
+      </c>
+      <c r="CO11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP11" s="14">
         <f t="shared" si="5"/>
-        <v>0.30447413548638541</v>
-      </c>
-      <c r="CL11" s="14">
+        <v>-0.33674066807072378</v>
+      </c>
+      <c r="CQ11" s="14">
         <f t="shared" si="6"/>
-        <v>4.5874458102961681E-2</v>
-      </c>
-      <c r="CM11" s="125">
+        <v>0.13487340397347147</v>
+      </c>
+      <c r="CR11" s="49">
         <f t="shared" si="7"/>
-        <v>0.46391469028240373</v>
-      </c>
-      <c r="CO11" s="120" t="s">
-        <v>10</v>
-      </c>
-      <c r="CP11" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.43814456999726642</v>
-      </c>
-      <c r="CQ11" s="14">
-        <f t="shared" si="9"/>
-        <v>0.25859967738342371</v>
-      </c>
-      <c r="CR11" s="49">
+        <v>3.2179592795721075E-3</v>
+      </c>
+      <c r="CS11" s="49">
+        <f t="shared" si="7"/>
+        <v>0.63188736481267072</v>
+      </c>
+      <c r="CU11" s="14"/>
+      <c r="CW11" s="119">
         <f t="shared" si="10"/>
-        <v>4.1915998463009528E-3</v>
-      </c>
-      <c r="CS11" s="131">
-        <f t="shared" si="10"/>
-        <v>0.72043781053215594</v>
-      </c>
-      <c r="CU11" s="14"/>
-      <c r="CW11" s="135">
-        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="CY11" s="14"/>
@@ -8492,25 +8408,25 @@
       <c r="R12" s="23">
         <v>0</v>
       </c>
-      <c r="T12" s="94"/>
-      <c r="U12" s="95">
+      <c r="T12" s="93"/>
+      <c r="U12" s="94">
         <v>20</v>
       </c>
-      <c r="V12" s="95">
+      <c r="V12" s="94">
         <v>56</v>
       </c>
-      <c r="W12" s="95">
+      <c r="W12" s="94">
         <v>2</v>
       </c>
-      <c r="X12" s="95">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="96"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="96"/>
-      <c r="AB12" s="96"/>
-      <c r="AC12" s="96"/>
-      <c r="AD12" s="97"/>
+      <c r="X12" s="94">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="95"/>
+      <c r="AA12" s="95"/>
+      <c r="AB12" s="95"/>
+      <c r="AC12" s="95"/>
+      <c r="AD12" s="96"/>
       <c r="AL12" s="39" t="s">
         <v>11</v>
       </c>
@@ -8526,7 +8442,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="80">
+      <c r="AP12" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8568,35 +8484,35 @@
         <v>10</v>
       </c>
       <c r="BE12" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="BF12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.16949152542372881</v>
       </c>
       <c r="BG12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI12" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ12" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="BK12" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.34615384615384615</v>
       </c>
       <c r="BL12" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM12" s="45"/>
@@ -8632,79 +8548,79 @@
         <v>9</v>
       </c>
       <c r="BZ12" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>6.3882063882063885E-3</v>
       </c>
       <c r="CA12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.14462251507706053</v>
+        <f t="shared" si="13"/>
+        <v>5.2432432432432431E-2</v>
       </c>
       <c r="CB12" s="13">
-        <f t="shared" si="16"/>
-        <v>6.7009157918248804E-4</v>
+        <f t="shared" si="13"/>
+        <v>3.2760032760032771E-3</v>
       </c>
       <c r="CC12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.11918695555059193</v>
+        <f t="shared" si="13"/>
+        <v>6.5025025025025038E-2</v>
       </c>
       <c r="CD12" s="13">
-        <f t="shared" si="16"/>
-        <v>2.2623652942801879E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.7512839325018339E-2</v>
       </c>
       <c r="CE12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.34725062171870674</v>
+        <f t="shared" si="13"/>
+        <v>0.32650665548684621</v>
       </c>
       <c r="CF12" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CG12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.21945288753799388</v>
-      </c>
-      <c r="CI12" s="120" t="s">
-        <v>11</v>
-      </c>
-      <c r="CJ12" s="124">
-        <f t="shared" si="4"/>
-        <v>4.2025160285219944E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.19276805366313801</v>
+      </c>
+      <c r="CI12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ12" s="14">
+        <f>(BZ21+CD21+BZ38+CD38)/$T$41</f>
+        <v>6.1007931999077485E-3</v>
       </c>
       <c r="CK12" s="14">
+        <f t="shared" ref="CK12:CM12" si="15">(CA21+CE21+CA38+CE38)/$T$41</f>
+        <v>0.26865586820989301</v>
+      </c>
+      <c r="CL12" s="14">
+        <f t="shared" si="15"/>
+        <v>5.5934610834540634E-2</v>
+      </c>
+      <c r="CM12" s="14">
+        <f t="shared" si="15"/>
+        <v>0.24561989347968777</v>
+      </c>
+      <c r="CO12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CP12" s="14">
         <f t="shared" si="5"/>
-        <v>0.33759164940962577</v>
-      </c>
-      <c r="CL12" s="14">
+        <v>-0.23951910027978002</v>
+      </c>
+      <c r="CQ12" s="14">
         <f t="shared" si="6"/>
-        <v>2.6109112249153937E-2</v>
-      </c>
-      <c r="CM12" s="125">
+        <v>0.21272125737535238</v>
+      </c>
+      <c r="CR12" s="49">
         <f t="shared" si="7"/>
-        <v>0.27457840010236501</v>
-      </c>
-      <c r="CO12" s="120" t="s">
-        <v>11</v>
-      </c>
-      <c r="CP12" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.23255323981714507</v>
-      </c>
-      <c r="CQ12" s="14">
-        <f t="shared" si="9"/>
-        <v>0.31148253716047181</v>
-      </c>
-      <c r="CR12" s="49">
+        <v>0.13281592687881044</v>
+      </c>
+      <c r="CS12" s="49">
+        <f t="shared" si="7"/>
+        <v>0.7356598487592525</v>
+      </c>
+      <c r="CU12" s="14"/>
+      <c r="CW12" s="119">
         <f t="shared" si="10"/>
-        <v>0.21553745845217631</v>
-      </c>
-      <c r="CS12" s="131">
-        <f t="shared" si="10"/>
-        <v>0.77480086852357211</v>
-      </c>
-      <c r="CU12" s="14"/>
-      <c r="CW12" s="135">
-        <f t="shared" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CY12" s="14"/>
     </row>
@@ -8760,25 +8676,25 @@
       <c r="R13" s="23">
         <v>7</v>
       </c>
-      <c r="T13" s="94"/>
-      <c r="U13" s="95">
+      <c r="T13" s="93"/>
+      <c r="U13" s="94">
         <v>28</v>
       </c>
-      <c r="V13" s="95">
+      <c r="V13" s="94">
         <v>60</v>
       </c>
-      <c r="W13" s="95">
+      <c r="W13" s="94">
         <v>2</v>
       </c>
-      <c r="X13" s="95">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="97"/>
+      <c r="X13" s="94">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="95"/>
+      <c r="Z13" s="95"/>
+      <c r="AA13" s="95"/>
+      <c r="AB13" s="95"/>
+      <c r="AC13" s="95"/>
+      <c r="AD13" s="96"/>
       <c r="AL13" s="39" t="s">
         <v>12</v>
       </c>
@@ -8794,7 +8710,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP13" s="80">
+      <c r="AP13" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8836,35 +8752,35 @@
         <v>11</v>
       </c>
       <c r="BE13" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BF13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="BI13" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BJ13" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="BK13" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL13" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM13" s="45"/>
@@ -8900,79 +8816,79 @@
         <v>10</v>
       </c>
       <c r="BZ13" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>5.3846153846153861E-3</v>
       </c>
       <c r="CA13" s="13">
+        <f t="shared" si="13"/>
+        <v>4.8125000000000001E-2</v>
+      </c>
+      <c r="CB13" s="13">
+        <f t="shared" si="13"/>
+        <v>6.0897435897435907E-3</v>
+      </c>
+      <c r="CC13" s="13">
+        <f t="shared" si="13"/>
+        <v>7.8425925925925927E-2</v>
+      </c>
+      <c r="CD13" s="13">
+        <f t="shared" si="13"/>
+        <v>5.3507728894173601E-2</v>
+      </c>
+      <c r="CE13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.16741973840665877</v>
+      </c>
+      <c r="CF13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.12332257516561917</v>
+      </c>
+      <c r="CG13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.30214030915576695</v>
+      </c>
+      <c r="CI13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ13" s="14">
+        <f>(BZ14+CD14+BZ31+CD31)/$T$41</f>
+        <v>5.6449671737073208E-2</v>
+      </c>
+      <c r="CK13" s="14">
+        <f t="shared" ref="CK13:CM19" si="16">(CA14+CE14+CA31+CE31)/$T$41</f>
+        <v>0.22023835226858454</v>
+      </c>
+      <c r="CL13" s="14">
         <f t="shared" si="16"/>
-        <v>0.13274147727272728</v>
-      </c>
-      <c r="CB13" s="13">
+        <v>7.9529025799004283E-2</v>
+      </c>
+      <c r="CM13" s="14">
         <f t="shared" si="16"/>
-        <v>1.2456293706293699E-3</v>
-      </c>
-      <c r="CC13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.14375000000000002</v>
-      </c>
-      <c r="CD13" s="13">
-        <f t="shared" si="16"/>
-        <v>4.3999104343931929E-2</v>
-      </c>
-      <c r="CE13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.17805642633228841</v>
-      </c>
-      <c r="CF13" s="13">
-        <f t="shared" si="16"/>
-        <v>7.586206896551724E-2</v>
-      </c>
-      <c r="CG13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.3439655172413793</v>
-      </c>
-      <c r="CI13" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="CJ13" s="124">
-        <f t="shared" si="4"/>
-        <v>1.7610042285314386E-2</v>
-      </c>
-      <c r="CK13" s="14">
+        <v>0.22372341905938201</v>
+      </c>
+      <c r="CO13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CP13" s="14">
         <f t="shared" si="5"/>
-        <v>0.35712157152575891</v>
-      </c>
-      <c r="CL13" s="14">
+        <v>-0.16727374732230879</v>
+      </c>
+      <c r="CQ13" s="14">
         <f t="shared" si="6"/>
-        <v>2.9449896530303995E-2</v>
-      </c>
-      <c r="CM13" s="125">
+        <v>0.14070932646958026</v>
+      </c>
+      <c r="CR13" s="49">
         <f t="shared" si="7"/>
-        <v>0.4598320831810801</v>
-      </c>
-      <c r="CO13" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="CP13" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.44222204089576572</v>
-      </c>
-      <c r="CQ13" s="14">
-        <f t="shared" si="9"/>
-        <v>0.32767167499545491</v>
-      </c>
-      <c r="CR13" s="49">
+        <v>0.22912018450928701</v>
+      </c>
+      <c r="CS13" s="49">
+        <f t="shared" si="7"/>
+        <v>0.63966674660775447</v>
+      </c>
+      <c r="CU13" s="14"/>
+      <c r="CW13" s="119">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="CS13" s="131">
-        <f t="shared" si="10"/>
-        <v>0.79144314246005465</v>
-      </c>
-      <c r="CU13" s="14"/>
-      <c r="CW13" s="135">
-        <f t="shared" si="13"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="CY13" s="14"/>
     </row>
@@ -9028,25 +8944,25 @@
       <c r="R14" s="23">
         <v>1</v>
       </c>
-      <c r="T14" s="94"/>
-      <c r="U14" s="95">
+      <c r="T14" s="93"/>
+      <c r="U14" s="94">
         <v>28</v>
       </c>
-      <c r="V14" s="95">
+      <c r="V14" s="94">
         <v>63</v>
       </c>
-      <c r="W14" s="95">
+      <c r="W14" s="94">
         <v>2</v>
       </c>
-      <c r="X14" s="95">
+      <c r="X14" s="94">
         <v>2</v>
       </c>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="97"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="95"/>
+      <c r="AA14" s="95"/>
+      <c r="AB14" s="95"/>
+      <c r="AC14" s="95"/>
+      <c r="AD14" s="96"/>
       <c r="AL14" s="39" t="s">
         <v>13</v>
       </c>
@@ -9062,7 +8978,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP14" s="80">
+      <c r="AP14" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9104,35 +9020,35 @@
         <v>12</v>
       </c>
       <c r="BE14" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BF14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="BI14" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="BJ14" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="BK14" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.61538461538461542</v>
       </c>
       <c r="BL14" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM14" s="45"/>
@@ -9168,79 +9084,79 @@
         <v>11</v>
       </c>
       <c r="BZ14" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.3078556263269639E-2</v>
       </c>
       <c r="CA14" s="13">
+        <f t="shared" si="13"/>
+        <v>7.2632696390658169E-2</v>
+      </c>
+      <c r="CB14" s="13">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="CC14" s="13">
+        <f t="shared" si="13"/>
+        <v>2.1797593772116095E-3</v>
+      </c>
+      <c r="CD14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.10715942477191896</v>
+      </c>
+      <c r="CE14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.30480903046234731</v>
+      </c>
+      <c r="CF14" s="13">
+        <f t="shared" si="13"/>
+        <v>6.0306169785062612E-2</v>
+      </c>
+      <c r="CG14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.20768517086748106</v>
+      </c>
+      <c r="CI14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="CJ14" s="14">
+        <f t="shared" ref="CJ14:CJ19" si="17">(BZ15+CD15+BZ32+CD32)/$T$41</f>
+        <v>2.1014872318464842E-2</v>
+      </c>
+      <c r="CK14" s="14">
         <f t="shared" si="16"/>
-        <v>0.20034018529241457</v>
-      </c>
-      <c r="CB14" s="13">
+        <v>0.29202644283918266</v>
+      </c>
+      <c r="CL14" s="14">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="CC14" s="13">
+        <v>5.6640575181394391E-2</v>
+      </c>
+      <c r="CM14" s="14">
         <f t="shared" si="16"/>
-        <v>3.9953676896352115E-3</v>
-      </c>
-      <c r="CD14" s="13">
-        <f t="shared" si="16"/>
-        <v>8.8116591928251109E-2</v>
-      </c>
-      <c r="CE14" s="13">
-        <f t="shared" si="16"/>
-        <v>0.32417448022829187</v>
-      </c>
-      <c r="CF14" s="13">
-        <f t="shared" si="16"/>
-        <v>3.709743171626579E-2</v>
-      </c>
-      <c r="CG14" s="13">
-        <f t="shared" si="16"/>
-        <v>0.23643497757847531</v>
-      </c>
-      <c r="CI14" s="120" t="s">
-        <v>13</v>
-      </c>
-      <c r="CJ14" s="124">
-        <f t="shared" si="4"/>
-        <v>3.2082349445582525E-2</v>
-      </c>
-      <c r="CK14" s="14">
+        <v>0.35740962575056262</v>
+      </c>
+      <c r="CO14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="CP14" s="14">
         <f t="shared" si="5"/>
-        <v>0.33879505132692134</v>
-      </c>
-      <c r="CL14" s="14">
+        <v>-0.33639475343209779</v>
+      </c>
+      <c r="CQ14" s="14">
         <f t="shared" si="6"/>
-        <v>2.2307958133356207E-2</v>
-      </c>
-      <c r="CM14" s="125">
+        <v>0.23538586765778827</v>
+      </c>
+      <c r="CR14" s="49">
         <f t="shared" si="7"/>
-        <v>0.36027146695670687</v>
-      </c>
-      <c r="CO14" s="120" t="s">
-        <v>13</v>
-      </c>
-      <c r="CP14" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.32818911751112434</v>
-      </c>
-      <c r="CQ14" s="14">
-        <f t="shared" si="9"/>
-        <v>0.31648709319356511</v>
-      </c>
-      <c r="CR14" s="49">
+        <v>3.6790692487628017E-3</v>
+      </c>
+      <c r="CS14" s="49">
+        <f t="shared" si="7"/>
+        <v>0.76587215139716669</v>
+      </c>
+      <c r="CU14" s="14"/>
+      <c r="CW14" s="119">
         <f t="shared" si="10"/>
-        <v>0.11722471993809447</v>
-      </c>
-      <c r="CS14" s="131">
-        <f t="shared" si="10"/>
-        <v>0.77994550273956109</v>
-      </c>
-      <c r="CU14" s="14"/>
-      <c r="CW14" s="135">
-        <f t="shared" si="13"/>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CY14" s="14"/>
     </row>
@@ -9296,25 +9212,25 @@
       <c r="R15" s="23">
         <v>1</v>
       </c>
-      <c r="T15" s="94"/>
-      <c r="U15" s="95">
+      <c r="T15" s="93"/>
+      <c r="U15" s="94">
         <v>51</v>
       </c>
-      <c r="V15" s="95">
+      <c r="V15" s="94">
         <v>66</v>
       </c>
-      <c r="W15" s="95">
+      <c r="W15" s="94">
         <v>3</v>
       </c>
-      <c r="X15" s="95">
+      <c r="X15" s="94">
         <v>5</v>
       </c>
-      <c r="Y15" s="96"/>
-      <c r="Z15" s="96"/>
-      <c r="AA15" s="96"/>
-      <c r="AB15" s="96"/>
-      <c r="AC15" s="96"/>
-      <c r="AD15" s="97"/>
+      <c r="Y15" s="95"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="95"/>
+      <c r="AB15" s="95"/>
+      <c r="AC15" s="95"/>
+      <c r="AD15" s="96"/>
       <c r="AL15" s="39" t="s">
         <v>14</v>
       </c>
@@ -9330,7 +9246,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="80">
+      <c r="AP15" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9372,35 +9288,35 @@
         <v>13</v>
       </c>
       <c r="BE15" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BF15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="BG15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="BI15" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.977491961414791</v>
       </c>
       <c r="BJ15" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.65536723163841804</v>
       </c>
       <c r="BK15" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL15" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM15" s="45"/>
@@ -9436,79 +9352,79 @@
         <v>12</v>
       </c>
       <c r="BZ15" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="CA15" s="13">
+        <f t="shared" si="13"/>
+        <v>3.6128330614464382E-2</v>
+      </c>
+      <c r="CB15" s="13">
+        <f t="shared" si="13"/>
+        <v>9.7879282218597211E-4</v>
+      </c>
+      <c r="CC15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.11574889734759231</v>
+      </c>
+      <c r="CD15" s="13">
+        <f t="shared" si="13"/>
+        <v>3.478391808462581E-2</v>
+      </c>
+      <c r="CE15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.19611504291522358</v>
+      </c>
+      <c r="CF15" s="13">
+        <f t="shared" si="13"/>
+        <v>9.3058274356271661E-2</v>
+      </c>
+      <c r="CG15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.28241228730612861</v>
+      </c>
+      <c r="CI15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CJ15" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA15" s="13">
+        <v>4.4028894465052454E-2</v>
+      </c>
+      <c r="CK15" s="14">
         <f t="shared" si="16"/>
-        <v>9.9651490434524689E-2</v>
-      </c>
-      <c r="CB15" s="13">
+        <v>0.24035222077580237</v>
+      </c>
+      <c r="CL15" s="14">
         <f t="shared" si="16"/>
-        <v>2.0020762271985779E-4</v>
-      </c>
-      <c r="CC15" s="13">
+        <v>6.6087665376814181E-2</v>
+      </c>
+      <c r="CM15" s="14">
         <f t="shared" si="16"/>
-        <v>0.21216075930594694</v>
-      </c>
-      <c r="CD15" s="13">
-        <f t="shared" si="16"/>
-        <v>2.8602620087336245E-2</v>
-      </c>
-      <c r="CE15" s="13">
-        <f t="shared" si="16"/>
-        <v>0.20857483128225482</v>
-      </c>
-      <c r="CF15" s="13">
-        <f t="shared" si="16"/>
-        <v>5.7244938467645889E-2</v>
-      </c>
-      <c r="CG15" s="13">
-        <f t="shared" si="16"/>
-        <v>0.32150655021834063</v>
-      </c>
-      <c r="CI15" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ15" s="124">
-        <f t="shared" si="4"/>
-        <v>3.2717535063552752E-2</v>
-      </c>
-      <c r="CK15" s="14">
+        <v>0.29651836962595829</v>
+      </c>
+      <c r="CO15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CP15" s="14">
         <f t="shared" si="5"/>
-        <v>0.27488690847136638</v>
-      </c>
-      <c r="CL15" s="14">
+        <v>-0.25248947516090581</v>
+      </c>
+      <c r="CQ15" s="14">
         <f t="shared" si="6"/>
-        <v>3.2516768556613569E-2</v>
-      </c>
-      <c r="CM15" s="125">
+        <v>0.17426455539898819</v>
+      </c>
+      <c r="CR15" s="49">
         <f t="shared" si="7"/>
-        <v>0.42026542460739558</v>
-      </c>
-      <c r="CO15" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP15" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.38754788954384284</v>
-      </c>
-      <c r="CQ15" s="14">
-        <f t="shared" si="9"/>
-        <v>0.24237013991475281</v>
-      </c>
-      <c r="CR15" s="49">
+        <v>0.1155262013396313</v>
+      </c>
+      <c r="CS15" s="49">
+        <f t="shared" si="7"/>
+        <v>0.68439642511828269</v>
+      </c>
+      <c r="CU15" s="14"/>
+      <c r="CW15" s="119">
         <f t="shared" si="10"/>
-        <v>5.6204488053538518E-2</v>
-      </c>
-      <c r="CS15" s="131">
-        <f t="shared" si="10"/>
-        <v>0.70375400617091488</v>
-      </c>
-      <c r="CU15" s="14"/>
-      <c r="CW15" s="135">
-        <f t="shared" si="13"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CY15" s="14"/>
     </row>
@@ -9564,25 +9480,25 @@
       <c r="R16" s="23">
         <v>1</v>
       </c>
-      <c r="T16" s="94"/>
-      <c r="U16" s="95">
+      <c r="T16" s="93"/>
+      <c r="U16" s="94">
         <v>52</v>
       </c>
-      <c r="V16" s="95">
+      <c r="V16" s="94">
         <v>70</v>
       </c>
-      <c r="W16" s="95">
+      <c r="W16" s="94">
         <v>4</v>
       </c>
-      <c r="X16" s="95">
+      <c r="X16" s="94">
         <v>6</v>
       </c>
-      <c r="Y16" s="96"/>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="96"/>
-      <c r="AB16" s="96"/>
-      <c r="AC16" s="96"/>
-      <c r="AD16" s="97"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="96"/>
       <c r="AL16" s="39" t="s">
         <v>15</v>
       </c>
@@ -9598,7 +9514,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP16" s="80">
+      <c r="AP16" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -9640,35 +9556,35 @@
         <v>14</v>
       </c>
       <c r="BE16" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="BF16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="BG16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI16" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.932475884244373</v>
       </c>
       <c r="BJ16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="BK16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BL16" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM16" s="45"/>
@@ -9704,79 +9620,79 @@
         <v>13</v>
       </c>
       <c r="BZ16" s="13">
+        <f t="shared" si="14"/>
+        <v>1.1975308641975308E-2</v>
+      </c>
+      <c r="CA16" s="13">
+        <f t="shared" si="13"/>
+        <v>6.8806584362139919E-2</v>
+      </c>
+      <c r="CB16" s="13">
+        <f t="shared" si="13"/>
+        <v>1.4403292181069955E-3</v>
+      </c>
+      <c r="CC16" s="13">
+        <f t="shared" si="13"/>
+        <v>1.4083219021490633E-2</v>
+      </c>
+      <c r="CD16" s="13">
+        <f t="shared" si="13"/>
+        <v>8.1806377146154963E-2</v>
+      </c>
+      <c r="CE16" s="13">
+        <f t="shared" si="13"/>
+        <v>0.29456066945606696</v>
+      </c>
+      <c r="CF16" s="13">
+        <f t="shared" si="13"/>
+        <v>5.2806232866830193E-2</v>
+      </c>
+      <c r="CG16" s="13">
+        <f t="shared" si="13"/>
+        <v>0.21473091905929878</v>
+      </c>
+      <c r="CI16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ16" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA16" s="13">
+        <v>4.3595168032908728E-2</v>
+      </c>
+      <c r="CK16" s="14">
         <f t="shared" si="16"/>
-        <v>0.18978675645342311</v>
-      </c>
-      <c r="CB16" s="13">
+        <v>0.18742867649124215</v>
+      </c>
+      <c r="CL16" s="14">
         <f t="shared" si="16"/>
-        <v>2.9461279461279432E-4</v>
-      </c>
-      <c r="CC16" s="13">
+        <v>8.8233052008642565E-2</v>
+      </c>
+      <c r="CM16" s="14">
         <f t="shared" si="16"/>
-        <v>2.5813692480359158E-2</v>
-      </c>
-      <c r="CD16" s="13">
-        <f t="shared" si="16"/>
-        <v>6.7268923545074188E-2</v>
-      </c>
-      <c r="CE16" s="13">
-        <f t="shared" si="16"/>
-        <v>0.31327500950931908</v>
-      </c>
-      <c r="CF16" s="13">
-        <f t="shared" si="16"/>
-        <v>3.2483834157474328E-2</v>
-      </c>
-      <c r="CG16" s="13">
-        <f t="shared" si="16"/>
-        <v>0.24445606694560665</v>
-      </c>
-      <c r="CI16" s="120" t="s">
-        <v>15</v>
-      </c>
-      <c r="CJ16" s="124">
-        <f t="shared" si="4"/>
-        <v>1.0922623244293763E-2</v>
-      </c>
-      <c r="CK16" s="14">
+        <v>0.34014061750135716</v>
+      </c>
+      <c r="CO16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP16" s="14">
         <f t="shared" si="5"/>
-        <v>0.30630179194131235</v>
-      </c>
-      <c r="CL16" s="14">
+        <v>-0.29654544946844841</v>
+      </c>
+      <c r="CQ16" s="14">
         <f t="shared" si="6"/>
-        <v>3.3195267604859552E-2</v>
-      </c>
-      <c r="CM16" s="125">
+        <v>9.9195624482599581E-2</v>
+      </c>
+      <c r="CR16" s="49">
         <f t="shared" si="7"/>
-        <v>0.34837338770362702</v>
-      </c>
-      <c r="CO16" s="120" t="s">
-        <v>15</v>
-      </c>
-      <c r="CP16" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.33745076445933325</v>
-      </c>
-      <c r="CQ16" s="14">
-        <f t="shared" si="9"/>
-        <v>0.27310652433645277</v>
-      </c>
-      <c r="CR16" s="49">
+        <v>5.6798854511208419E-2</v>
+      </c>
+      <c r="CS16" s="49">
+        <f t="shared" si="7"/>
+        <v>0.58432829108518969</v>
+      </c>
+      <c r="CU16" s="14"/>
+      <c r="CW16" s="119">
         <f t="shared" si="10"/>
-        <v>0.10770383827125189</v>
-      </c>
-      <c r="CS16" s="131">
-        <f t="shared" si="10"/>
-        <v>0.73535070604319641</v>
-      </c>
-      <c r="CU16" s="14"/>
-      <c r="CW16" s="135">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CY16" s="14"/>
     </row>
@@ -9832,25 +9748,25 @@
       <c r="R17" s="23">
         <v>2</v>
       </c>
-      <c r="T17" s="94"/>
-      <c r="U17" s="95">
+      <c r="T17" s="93"/>
+      <c r="U17" s="94">
         <v>79</v>
       </c>
-      <c r="V17" s="95">
+      <c r="V17" s="94">
         <v>72</v>
       </c>
-      <c r="W17" s="95">
+      <c r="W17" s="94">
         <v>8</v>
       </c>
-      <c r="X17" s="95">
+      <c r="X17" s="94">
         <v>6</v>
       </c>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="97"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="96"/>
       <c r="AL17" s="39" t="s">
         <v>16</v>
       </c>
@@ -9866,7 +9782,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP17" s="80">
+      <c r="AP17" s="79">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -9908,35 +9824,35 @@
         <v>15</v>
       </c>
       <c r="BE17" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BF17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.10169491525423729</v>
       </c>
       <c r="BG17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI17" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BJ17" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="BK17" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL17" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM17" s="45"/>
@@ -9972,79 +9888,79 @@
         <v>14</v>
       </c>
       <c r="BZ17" s="13">
+        <f t="shared" si="14"/>
+        <v>9.4318181818181818E-3</v>
+      </c>
+      <c r="CA17" s="13">
+        <f t="shared" si="13"/>
+        <v>6.0416666666666667E-2</v>
+      </c>
+      <c r="CB17" s="13">
+        <f t="shared" si="13"/>
+        <v>3.9772727272727269E-3</v>
+      </c>
+      <c r="CC17" s="13">
+        <f t="shared" si="13"/>
+        <v>4.0185185185185192E-2</v>
+      </c>
+      <c r="CD17" s="13">
+        <f t="shared" si="13"/>
+        <v>8.3426028921023368E-2</v>
+      </c>
+      <c r="CE17" s="13">
+        <f t="shared" si="13"/>
+        <v>0.25170824725885904</v>
+      </c>
+      <c r="CF17" s="13">
+        <f t="shared" si="13"/>
+        <v>8.294930875576037E-2</v>
+      </c>
+      <c r="CG17" s="13">
+        <f t="shared" si="13"/>
+        <v>0.24419195931987925</v>
+      </c>
+      <c r="CI17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ17" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA17" s="13">
+        <v>1.9000912343798849E-2</v>
+      </c>
+      <c r="CK17" s="14">
         <f t="shared" si="16"/>
-        <v>0.16664514462809918</v>
-      </c>
-      <c r="CB17" s="13">
+        <v>0.20197178721593592</v>
+      </c>
+      <c r="CL17" s="14">
         <f t="shared" si="16"/>
-        <v>8.1353305785123895E-4</v>
-      </c>
-      <c r="CC17" s="13">
+        <v>8.3255735944985865E-2</v>
+      </c>
+      <c r="CM17" s="14">
         <f t="shared" si="16"/>
-        <v>7.365702479338844E-2</v>
-      </c>
-      <c r="CD17" s="13">
-        <f t="shared" si="16"/>
-        <v>6.8600754084625057E-2</v>
-      </c>
-      <c r="CE17" s="13">
-        <f t="shared" si="16"/>
-        <v>0.26770004189359026</v>
-      </c>
-      <c r="CF17" s="13">
-        <f t="shared" si="16"/>
-        <v>5.1026392961876832E-2</v>
-      </c>
-      <c r="CG17" s="13">
-        <f t="shared" si="16"/>
-        <v>0.27799539170506909</v>
-      </c>
-      <c r="CI17" s="120" t="s">
-        <v>16</v>
-      </c>
-      <c r="CJ17" s="124">
-        <f t="shared" si="4"/>
-        <v>2.5242463774803235E-2</v>
-      </c>
-      <c r="CK17" s="14">
+        <v>0.28783920757609516</v>
+      </c>
+      <c r="CO17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="CP17" s="14">
         <f t="shared" si="5"/>
-        <v>0.37253416325818794</v>
-      </c>
-      <c r="CL17" s="14">
+        <v>-0.2688382952322963</v>
+      </c>
+      <c r="CQ17" s="14">
         <f t="shared" si="6"/>
-        <v>3.1390482648606548E-2</v>
-      </c>
-      <c r="CM17" s="125">
+        <v>0.11871605127095006</v>
+      </c>
+      <c r="CR17" s="49">
         <f t="shared" si="7"/>
-        <v>0.4459699575572858</v>
-      </c>
-      <c r="CO17" s="120" t="s">
-        <v>16</v>
-      </c>
-      <c r="CP17" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.42072749378248259</v>
-      </c>
-      <c r="CQ17" s="14">
-        <f t="shared" si="9"/>
-        <v>0.34114368060958139</v>
-      </c>
-      <c r="CR17" s="49">
+        <v>9.373295214564735E-2</v>
+      </c>
+      <c r="CS17" s="49">
+        <f t="shared" si="7"/>
+        <v>0.61034934480734138</v>
+      </c>
+      <c r="CU17" s="14"/>
+      <c r="CW17" s="119">
         <f t="shared" si="10"/>
-        <v>2.209618231965944E-2</v>
-      </c>
-      <c r="CS17" s="131">
-        <f t="shared" si="10"/>
-        <v>0.8052922312867391</v>
-      </c>
-      <c r="CU17" s="14"/>
-      <c r="CW17" s="135">
-        <f t="shared" si="13"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CY17" s="14"/>
     </row>
@@ -10100,25 +10016,25 @@
       <c r="R18" s="23">
         <v>0</v>
       </c>
-      <c r="T18" s="94"/>
-      <c r="U18" s="95">
+      <c r="T18" s="93"/>
+      <c r="U18" s="94">
         <v>108</v>
       </c>
-      <c r="V18" s="95">
+      <c r="V18" s="94">
         <v>90</v>
       </c>
-      <c r="W18" s="95">
+      <c r="W18" s="94">
         <v>15</v>
       </c>
-      <c r="X18" s="95">
+      <c r="X18" s="94">
         <v>9</v>
       </c>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="96"/>
-      <c r="AD18" s="97"/>
+      <c r="Y18" s="95"/>
+      <c r="Z18" s="95"/>
+      <c r="AA18" s="95"/>
+      <c r="AB18" s="95"/>
+      <c r="AC18" s="95"/>
+      <c r="AD18" s="96"/>
       <c r="AL18" s="39" t="s">
         <v>17</v>
       </c>
@@ -10134,7 +10050,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="80">
+      <c r="AP18" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10176,35 +10092,35 @@
         <v>16</v>
       </c>
       <c r="BE18" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.57234726688102899</v>
       </c>
       <c r="BF18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.19209039548022599</v>
       </c>
       <c r="BG18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BI18" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ18" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="BK18" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.57692307692307687</v>
       </c>
       <c r="BL18" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM18" s="45"/>
@@ -10240,79 +10156,79 @@
         <v>15</v>
       </c>
       <c r="BZ18" s="13">
+        <f t="shared" si="14"/>
+        <v>1.2620545073375263E-2</v>
+      </c>
+      <c r="CA18" s="13">
+        <f t="shared" si="13"/>
+        <v>7.1027253668763099E-2</v>
+      </c>
+      <c r="CB18" s="13">
+        <f t="shared" si="13"/>
+        <v>6.2893081761006384E-4</v>
+      </c>
+      <c r="CC18" s="13">
+        <f t="shared" si="13"/>
+        <v>7.1744700675518318E-3</v>
+      </c>
+      <c r="CD18" s="13">
+        <f t="shared" si="13"/>
+        <v>2.7851458885941646E-2</v>
+      </c>
+      <c r="CE18" s="13">
+        <f t="shared" si="13"/>
+        <v>0.19451812555260828</v>
+      </c>
+      <c r="CF18" s="13">
+        <f t="shared" si="13"/>
+        <v>9.0185676392572939E-2</v>
+      </c>
+      <c r="CG18" s="13">
+        <f t="shared" si="13"/>
+        <v>0.28351016799292661</v>
+      </c>
+      <c r="CI18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ18" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA18" s="13">
+        <v>3.28946275943027E-2</v>
+      </c>
+      <c r="CK18" s="14">
         <f t="shared" si="16"/>
-        <v>0.1959119496855346</v>
-      </c>
-      <c r="CB18" s="13">
+        <v>0.30078349509117125</v>
+      </c>
+      <c r="CL18" s="14">
         <f t="shared" si="16"/>
-        <v>1.2864493996569477E-4</v>
-      </c>
-      <c r="CC18" s="13">
+        <v>6.5011316059009658E-2</v>
+      </c>
+      <c r="CM18" s="14">
         <f t="shared" si="16"/>
-        <v>1.3150371640937686E-2</v>
-      </c>
-      <c r="CD18" s="13">
-        <f t="shared" si="16"/>
-        <v>2.2902097902097903E-2</v>
-      </c>
-      <c r="CE18" s="13">
-        <f t="shared" si="16"/>
-        <v>0.20687645687645684</v>
-      </c>
-      <c r="CF18" s="13">
-        <f t="shared" si="16"/>
-        <v>5.547785547785547E-2</v>
-      </c>
-      <c r="CG18" s="13">
-        <f t="shared" si="16"/>
-        <v>0.32275641025641028</v>
-      </c>
-      <c r="CI18" s="120" t="s">
-        <v>17</v>
-      </c>
-      <c r="CJ18" s="124">
-        <f t="shared" si="4"/>
-        <v>5.7825652469790526E-3</v>
-      </c>
-      <c r="CK18" s="14">
+        <v>0.35723336977976639</v>
+      </c>
+      <c r="CO18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CP18" s="14">
         <f t="shared" si="5"/>
-        <v>0.2495748515035994</v>
-      </c>
-      <c r="CL18" s="14">
+        <v>-0.32433874218546366</v>
+      </c>
+      <c r="CQ18" s="14">
         <f t="shared" si="6"/>
-        <v>4.1928830388223058E-2</v>
-      </c>
-      <c r="CM18" s="125">
+        <v>0.23577217903216158</v>
+      </c>
+      <c r="CR18" s="49">
         <f t="shared" si="7"/>
-        <v>0.38657394328072581</v>
-      </c>
-      <c r="CO18" s="120" t="s">
-        <v>17</v>
-      </c>
-      <c r="CP18" s="124">
-        <f t="shared" si="8"/>
-        <v>-0.38079137803374674</v>
-      </c>
-      <c r="CQ18" s="14">
-        <f t="shared" si="9"/>
-        <v>0.20764602111537633</v>
-      </c>
-      <c r="CR18" s="49">
+        <v>1.9749932848463825E-2</v>
+      </c>
+      <c r="CS18" s="49">
+        <f t="shared" si="7"/>
+        <v>0.76638711088729661</v>
+      </c>
+      <c r="CU18" s="14"/>
+      <c r="CW18" s="119">
         <f t="shared" si="10"/>
-        <v>6.3150115211214303E-2</v>
-      </c>
-      <c r="CS18" s="131">
-        <f t="shared" si="10"/>
-        <v>0.66805795471019902</v>
-      </c>
-      <c r="CU18" s="14"/>
-      <c r="CW18" s="135">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CY18" s="14"/>
     </row>
@@ -10320,7 +10236,7 @@
       <c r="A19" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="24">
@@ -10368,41 +10284,41 @@
       <c r="R19" s="23">
         <v>0</v>
       </c>
-      <c r="T19" s="94"/>
-      <c r="U19" s="95">
+      <c r="T19" s="93"/>
+      <c r="U19" s="94">
         <v>116</v>
       </c>
-      <c r="V19" s="95">
+      <c r="V19" s="94">
         <v>96</v>
       </c>
-      <c r="W19" s="95">
+      <c r="W19" s="94">
         <v>26</v>
       </c>
-      <c r="X19" s="95">
+      <c r="X19" s="94">
         <v>9</v>
       </c>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96"/>
-      <c r="AB19" s="96"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="97"/>
-      <c r="AL19" s="73" t="s">
+      <c r="Y19" s="95"/>
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="95"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="95"/>
+      <c r="AD19" s="96"/>
+      <c r="AL19" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM19" s="84">
+      <c r="AM19" s="83">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN19" s="85">
+      <c r="AN19" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="85">
+      <c r="AO19" s="84">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="86">
+      <c r="AP19" s="85">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10444,35 +10360,35 @@
         <v>17</v>
       </c>
       <c r="BE19" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="BF19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>5.0847457627118647E-2</v>
       </c>
       <c r="BG19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI19" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ19" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="BK19" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BL19" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM19" s="45"/>
@@ -10508,79 +10424,79 @@
         <v>16</v>
       </c>
       <c r="BZ19" s="13">
+        <f t="shared" si="14"/>
+        <v>5.8456486042692954E-3</v>
+      </c>
+      <c r="CA19" s="13">
+        <f t="shared" si="13"/>
+        <v>4.9310344827586214E-2</v>
+      </c>
+      <c r="CB19" s="13">
+        <f t="shared" si="13"/>
+        <v>6.2397372742200334E-3</v>
+      </c>
+      <c r="CC19" s="13">
+        <f t="shared" si="13"/>
+        <v>7.4738186462324399E-2</v>
+      </c>
+      <c r="CD19" s="13">
+        <f t="shared" si="13"/>
+        <v>5.3992740471869333E-2</v>
+      </c>
+      <c r="CE19" s="13">
+        <f t="shared" si="13"/>
+        <v>0.22625529340592865</v>
+      </c>
+      <c r="CF19" s="13">
+        <f t="shared" si="13"/>
+        <v>8.3484573502722328E-2</v>
+      </c>
+      <c r="CG19" s="13">
+        <f t="shared" si="13"/>
+        <v>0.26169086509376893</v>
+      </c>
+      <c r="CI19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CJ19" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA19" s="13">
+        <v>1.2279935306048814E-2</v>
+      </c>
+      <c r="CK19" s="14">
         <f t="shared" si="16"/>
-        <v>0.13601097178683388</v>
-      </c>
-      <c r="CB19" s="13">
+        <v>0.1503526853852121</v>
+      </c>
+      <c r="CL19" s="14">
         <f t="shared" si="16"/>
-        <v>1.2763098969995515E-3</v>
-      </c>
-      <c r="CC19" s="13">
+        <v>0.10229921511203946</v>
+      </c>
+      <c r="CM19" s="14">
         <f t="shared" si="16"/>
-        <v>0.13699059561128527</v>
-      </c>
-      <c r="CD19" s="13">
-        <f t="shared" si="16"/>
-        <v>4.4397926634768749E-2</v>
-      </c>
-      <c r="CE19" s="13">
-        <f t="shared" si="16"/>
-        <v>0.24062998405103669</v>
-      </c>
-      <c r="CF19" s="13">
-        <f t="shared" si="16"/>
-        <v>5.1355661881977668E-2</v>
-      </c>
-      <c r="CG19" s="13">
-        <f t="shared" si="16"/>
-        <v>0.29791666666666666</v>
-      </c>
-      <c r="CI19" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ19" s="126">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="CK19" s="127">
+        <v>0.31695529615120233</v>
+      </c>
+      <c r="CO19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CP19" s="14">
         <f t="shared" si="5"/>
-        <v>0.37922230947871016</v>
-      </c>
-      <c r="CL19" s="127">
+        <v>-0.30467536084515351</v>
+      </c>
+      <c r="CQ19" s="14">
         <f t="shared" si="6"/>
-        <v>2.2465538624545461E-2</v>
-      </c>
-      <c r="CM19" s="128">
+        <v>4.8053470273172638E-2</v>
+      </c>
+      <c r="CR19" s="49">
         <f t="shared" si="7"/>
-        <v>0.29633621175559954</v>
-      </c>
-      <c r="CO19" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="CP19" s="126">
-        <f t="shared" si="8"/>
-        <v>-0.29633621175559954</v>
-      </c>
-      <c r="CQ19" s="127">
-        <f t="shared" si="9"/>
-        <v>0.35675677085416468</v>
-      </c>
-      <c r="CR19" s="132">
+        <v>4.5961547367092896E-2</v>
+      </c>
+      <c r="CS19" s="49">
+        <f t="shared" si="7"/>
+        <v>0.51615494853592514</v>
+      </c>
+      <c r="CU19" s="14"/>
+      <c r="CW19" s="120">
         <f t="shared" si="10"/>
-        <v>0.14996919272347622</v>
-      </c>
-      <c r="CS19" s="133">
-        <f t="shared" si="10"/>
-        <v>0.82134233398485135</v>
-      </c>
-      <c r="CU19" s="14"/>
-      <c r="CW19" s="136">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CY19" s="14"/>
     </row>
@@ -10636,33 +10552,33 @@
       <c r="R20" s="23">
         <v>2</v>
       </c>
-      <c r="T20" s="94"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="96"/>
-      <c r="W20" s="96"/>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="97"/>
+      <c r="T20" s="93"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="96"/>
       <c r="AL20" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM20" s="77">
+      <c r="AM20" s="76">
         <f t="shared" si="0"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN20" s="78">
+      <c r="AN20" s="77">
         <f t="shared" si="1"/>
         <v>0.24293785310734464</v>
       </c>
-      <c r="AO20" s="78">
+      <c r="AO20" s="77">
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP20" s="79">
+      <c r="AP20" s="78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10704,35 +10620,35 @@
         <v>21</v>
       </c>
       <c r="BE20" s="54">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="BF20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BG20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="BI20" s="54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BJ20" s="54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.5423728813559322</v>
       </c>
       <c r="BK20" s="54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="BL20" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM20" s="45"/>
@@ -10768,36 +10684,36 @@
         <v>17</v>
       </c>
       <c r="BZ20" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.141141141141141E-2</v>
       </c>
       <c r="CA20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.18647966147966144</v>
+        <f t="shared" si="13"/>
+        <v>6.7607607607607603E-2</v>
       </c>
       <c r="CB20" s="13">
-        <f t="shared" si="16"/>
-        <v>1.6380016380016343E-4</v>
+        <f t="shared" si="13"/>
+        <v>8.0080080080079954E-4</v>
       </c>
       <c r="CC20" s="13">
-        <f t="shared" si="16"/>
-        <v>3.2650832650832663E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.7813368924480044E-2</v>
       </c>
       <c r="CD20" s="13">
-        <f t="shared" si="16"/>
-        <v>1.2124640065816539E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4744889998439698E-2</v>
       </c>
       <c r="CE20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.15479226655697245</v>
+        <f t="shared" si="13"/>
+        <v>0.14554532688406929</v>
       </c>
       <c r="CF20" s="13">
-        <f t="shared" si="16"/>
-        <v>7.1410941999177288E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.1160867530035887</v>
       </c>
       <c r="CG20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.36108597285067873</v>
+        <f t="shared" si="13"/>
+        <v>0.31717896707754722</v>
       </c>
       <c r="CR20" s="13"/>
       <c r="CS20" s="13"/>
@@ -10854,19 +10770,19 @@
       <c r="R21" s="23">
         <v>0</v>
       </c>
-      <c r="T21" s="99" t="s">
+      <c r="T21" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="U21" s="96"/>
-      <c r="V21" s="96"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="96"/>
-      <c r="Y21" s="96"/>
-      <c r="Z21" s="96"/>
-      <c r="AA21" s="96"/>
-      <c r="AB21" s="96"/>
-      <c r="AC21" s="96"/>
-      <c r="AD21" s="97"/>
+      <c r="U21" s="95"/>
+      <c r="V21" s="95"/>
+      <c r="W21" s="95"/>
+      <c r="X21" s="95"/>
+      <c r="Y21" s="95"/>
+      <c r="Z21" s="95"/>
+      <c r="AA21" s="95"/>
+      <c r="AB21" s="95"/>
+      <c r="AC21" s="95"/>
+      <c r="AD21" s="96"/>
       <c r="AL21" s="39" t="s">
         <v>2</v>
       </c>
@@ -10882,7 +10798,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP21" s="80">
+      <c r="AP21" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10920,21 +10836,21 @@
         <v>0</v>
       </c>
       <c r="BC21" s="45"/>
-      <c r="BD21" s="144" t="s">
+      <c r="BD21" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="BE21" s="146" t="s">
+      <c r="BE21" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="BF21" s="146"/>
-      <c r="BG21" s="146"/>
-      <c r="BH21" s="146"/>
-      <c r="BI21" s="146" t="s">
+      <c r="BF21" s="131"/>
+      <c r="BG21" s="131"/>
+      <c r="BH21" s="131"/>
+      <c r="BI21" s="131" t="s">
         <v>112</v>
       </c>
-      <c r="BJ21" s="146"/>
-      <c r="BK21" s="146"/>
-      <c r="BL21" s="147"/>
+      <c r="BJ21" s="131"/>
+      <c r="BK21" s="131"/>
+      <c r="BL21" s="132"/>
       <c r="BM21" s="45"/>
       <c r="BN21" s="45"/>
       <c r="BO21" s="4" t="s">
@@ -10968,44 +10884,44 @@
         <v>21</v>
       </c>
       <c r="BZ21" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.2994708994708996E-2</v>
       </c>
       <c r="CA21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.19970418470418475</v>
+        <f t="shared" si="13"/>
+        <v>7.2402116402116412E-2</v>
       </c>
       <c r="CB21" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CC21" s="13">
-        <f t="shared" si="16"/>
-        <v>5.3102453102453042E-3</v>
+        <f t="shared" si="13"/>
+        <v>2.8971193415637825E-3</v>
       </c>
       <c r="CD21" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CE21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.22697302697302696</v>
+        <f t="shared" si="13"/>
+        <v>0.21341417203486171</v>
       </c>
       <c r="CF21" s="13">
-        <f t="shared" si="16"/>
-        <v>3.7762237762237756E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.1386888973095868E-2</v>
       </c>
       <c r="CG21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.30796703296703298</v>
+        <f t="shared" si="13"/>
+        <v>0.27051913603637745</v>
       </c>
       <c r="CP21" s="13">
         <f>ABS(MIN(CP4:CP19))</f>
-        <v>0.44222204089576572</v>
+        <v>0.33915471091447325</v>
       </c>
       <c r="CQ21" s="13">
         <f>MAX(CQ4:CQ19)</f>
-        <v>0.53054994307537406</v>
+        <v>0.41102347159828362</v>
       </c>
     </row>
     <row r="22" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11060,31 +10976,31 @@
       <c r="R22" s="23">
         <v>1</v>
       </c>
-      <c r="T22" s="99" t="s">
+      <c r="T22" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="U22" s="96">
+      <c r="U22" s="95">
         <f>MIN(U4:U8)</f>
         <v>2</v>
       </c>
-      <c r="V22" s="96">
+      <c r="V22" s="95">
         <f>MIN(V16:V19)</f>
         <v>70</v>
       </c>
-      <c r="W22" s="96">
+      <c r="W22" s="95">
         <f>MIN(W18:W19)</f>
         <v>15</v>
       </c>
-      <c r="X22" s="96">
+      <c r="X22" s="95">
         <f>MIN(X4:X13)</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="96"/>
-      <c r="Z22" s="96"/>
-      <c r="AA22" s="96"/>
-      <c r="AB22" s="96"/>
-      <c r="AC22" s="96"/>
-      <c r="AD22" s="97"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="95"/>
+      <c r="AA22" s="95"/>
+      <c r="AB22" s="95"/>
+      <c r="AC22" s="95"/>
+      <c r="AD22" s="96"/>
       <c r="AL22" s="39" t="s">
         <v>4</v>
       </c>
@@ -11100,7 +11016,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="80">
+      <c r="AP22" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -11138,7 +11054,7 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="BC22" s="45"/>
-      <c r="BD22" s="145"/>
+      <c r="BD22" s="130"/>
       <c r="BE22" s="47" t="s">
         <v>64</v>
       </c>
@@ -11270,31 +11186,31 @@
       <c r="R23" s="23">
         <v>1</v>
       </c>
-      <c r="T23" s="99" t="s">
-        <v>37</v>
-      </c>
-      <c r="U23" s="96">
+      <c r="T23" s="98" t="s">
+        <v>107</v>
+      </c>
+      <c r="U23" s="95">
         <f>MIN(U9:U14)</f>
         <v>10</v>
       </c>
-      <c r="V23" s="96">
+      <c r="V23" s="95">
         <f>MIN(V9:V15)</f>
         <v>40</v>
       </c>
-      <c r="W23" s="96">
+      <c r="W23" s="95">
         <f>MIN(W16:W17)</f>
         <v>4</v>
       </c>
-      <c r="X23" s="96">
+      <c r="X23" s="95">
         <f>MIN(X14:X15)</f>
         <v>2</v>
       </c>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="96"/>
-      <c r="AA23" s="96"/>
-      <c r="AB23" s="96"/>
-      <c r="AC23" s="96"/>
-      <c r="AD23" s="97"/>
+      <c r="Y23" s="95"/>
+      <c r="Z23" s="95"/>
+      <c r="AA23" s="95"/>
+      <c r="AB23" s="95"/>
+      <c r="AC23" s="95"/>
+      <c r="AD23" s="96"/>
       <c r="AL23" s="39" t="s">
         <v>5</v>
       </c>
@@ -11310,7 +11226,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="80">
+      <c r="AP23" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11386,40 +11302,40 @@
       <c r="BM23" s="45"/>
       <c r="BN23" s="45"/>
       <c r="BO23" s="38"/>
-      <c r="BP23" s="137" t="s">
+      <c r="BP23" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="BQ23" s="137"/>
-      <c r="BR23" s="137" t="s">
+      <c r="BQ23" s="122"/>
+      <c r="BR23" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="BS23" s="137"/>
-      <c r="BT23" s="137" t="s">
+      <c r="BS23" s="122"/>
+      <c r="BT23" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="BU23" s="137"/>
-      <c r="BV23" s="137" t="s">
+      <c r="BU23" s="122"/>
+      <c r="BV23" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="BW23" s="137"/>
+      <c r="BW23" s="122"/>
       <c r="BY23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="BZ23" s="13">
         <f t="shared" ref="BZ23:CG38" si="20">BP27*BP$24</f>
-        <v>1.1005692599620493E-2</v>
+        <v>1.3196480938416421E-2</v>
       </c>
       <c r="CA23" s="13">
         <f t="shared" si="20"/>
-        <v>0.16736242884250474</v>
+        <v>0.16774193548387098</v>
       </c>
       <c r="CB23" s="13">
         <f t="shared" si="20"/>
-        <v>1.1385199240986712E-2</v>
+        <v>7.0381231671554259E-2</v>
       </c>
       <c r="CC23" s="13">
         <f t="shared" si="20"/>
-        <v>0.27039848197343458</v>
+        <v>0.21505376344086027</v>
       </c>
       <c r="CD23" s="13">
         <f t="shared" si="20"/>
@@ -11427,7 +11343,7 @@
       </c>
       <c r="CE23" s="13">
         <f t="shared" si="20"/>
-        <v>0.13749999999999998</v>
+        <v>6.8749999999999992E-2</v>
       </c>
       <c r="CF23" s="13">
         <f t="shared" si="20"/>
@@ -11435,7 +11351,7 @@
       </c>
       <c r="CG23" s="13">
         <f t="shared" si="20"/>
-        <v>0.12916666666666668</v>
+        <v>0.11458333333333334</v>
       </c>
     </row>
     <row r="24" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11490,31 +11406,31 @@
       <c r="R24" s="23">
         <v>1</v>
       </c>
-      <c r="T24" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="U24" s="96">
+      <c r="T24" s="98" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" s="95">
         <f>MIN(U15:U19)</f>
         <v>51</v>
       </c>
-      <c r="V24" s="96">
+      <c r="V24" s="95">
         <f>MIN(V4:V8)</f>
         <v>14</v>
       </c>
-      <c r="W24" s="96">
+      <c r="W24" s="95">
         <f>MIN(W4:W15)</f>
         <v>0</v>
       </c>
-      <c r="X24" s="96">
+      <c r="X24" s="95">
         <f>MIN(X16:X19)</f>
         <v>6</v>
       </c>
-      <c r="Y24" s="96"/>
-      <c r="Z24" s="96"/>
-      <c r="AA24" s="96"/>
-      <c r="AB24" s="96"/>
-      <c r="AC24" s="96"/>
-      <c r="AD24" s="97"/>
+      <c r="Y24" s="95"/>
+      <c r="Z24" s="95"/>
+      <c r="AA24" s="95"/>
+      <c r="AB24" s="95"/>
+      <c r="AC24" s="95"/>
+      <c r="AD24" s="96"/>
       <c r="AL24" s="39" t="s">
         <v>6</v>
       </c>
@@ -11530,7 +11446,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP24" s="80">
+      <c r="AP24" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11606,48 +11522,48 @@
       <c r="BM24" s="45"/>
       <c r="BN24" s="45"/>
       <c r="BO24" s="30"/>
-      <c r="BP24" s="117">
+      <c r="BP24" s="115">
         <f>AC37</f>
-        <v>0.3411764705882353</v>
-      </c>
-      <c r="BQ24" s="118">
+        <v>0.40909090909090906</v>
+      </c>
+      <c r="BQ24" s="116">
         <f>AC38</f>
-        <v>0.8647058823529411</v>
-      </c>
-      <c r="BR24" s="118">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BR24" s="116">
         <f>AC39</f>
-        <v>1.7647058823529405E-2</v>
-      </c>
-      <c r="BS24" s="118">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="BS24" s="116">
         <f>AC40</f>
-        <v>0.33529411764705885</v>
-      </c>
-      <c r="BT24" s="118">
+        <v>0.26666666666666672</v>
+      </c>
+      <c r="BT24" s="116">
         <f>AD37</f>
         <v>0</v>
       </c>
-      <c r="BU24" s="118">
+      <c r="BU24" s="116">
         <f>AD38</f>
-        <v>0.18333333333333335</v>
-      </c>
-      <c r="BV24" s="118">
+        <v>9.1666666666666674E-2</v>
+      </c>
+      <c r="BV24" s="116">
         <f>AD39</f>
-        <v>6.6666666666666652E-2</v>
-      </c>
-      <c r="BW24" s="119">
+        <v>0.15</v>
+      </c>
+      <c r="BW24" s="117">
         <f>AD40</f>
-        <v>0.51666666666666672</v>
+        <v>0.45833333333333337</v>
       </c>
       <c r="BY24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="BZ24" s="13">
         <f t="shared" si="20"/>
-        <v>1.3647058823529413E-2</v>
+        <v>1.6363636363636361E-2</v>
       </c>
       <c r="CA24" s="13">
         <f t="shared" si="20"/>
-        <v>0.4496470588235294</v>
+        <v>0.45066666666666672</v>
       </c>
       <c r="CB24" s="13">
         <f t="shared" si="20"/>
@@ -11655,7 +11571,7 @@
       </c>
       <c r="CC24" s="13">
         <f t="shared" si="20"/>
-        <v>0.16094117647058825</v>
+        <v>0.12800000000000003</v>
       </c>
       <c r="CD24" s="13">
         <f t="shared" si="20"/>
@@ -11663,7 +11579,7 @@
       </c>
       <c r="CE24" s="13">
         <f t="shared" si="20"/>
-        <v>0.16500000000000001</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="CF24" s="13">
         <f t="shared" si="20"/>
@@ -11671,7 +11587,7 @@
       </c>
       <c r="CG24" s="13">
         <f t="shared" si="20"/>
-        <v>5.1666666666666687E-2</v>
+        <v>4.5833333333333351E-2</v>
       </c>
     </row>
     <row r="25" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11726,17 +11642,17 @@
       <c r="R25" s="23">
         <v>1</v>
       </c>
-      <c r="T25" s="99"/>
-      <c r="U25" s="96"/>
-      <c r="V25" s="96"/>
-      <c r="W25" s="96"/>
-      <c r="X25" s="96"/>
-      <c r="Y25" s="96"/>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="96"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-      <c r="AD25" s="97"/>
+      <c r="T25" s="98"/>
+      <c r="U25" s="95"/>
+      <c r="V25" s="95"/>
+      <c r="W25" s="95"/>
+      <c r="X25" s="95"/>
+      <c r="Y25" s="95"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="95"/>
+      <c r="AB25" s="95"/>
+      <c r="AC25" s="95"/>
+      <c r="AD25" s="96"/>
       <c r="AL25" s="39" t="s">
         <v>8</v>
       </c>
@@ -11752,7 +11668,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP25" s="80">
+      <c r="AP25" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11828,22 +11744,22 @@
       <c r="BM25" s="45"/>
       <c r="BN25" s="45"/>
       <c r="BO25" s="30"/>
-      <c r="BP25" s="142" t="s">
+      <c r="BP25" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="BQ25" s="143"/>
-      <c r="BR25" s="142" t="s">
+      <c r="BQ25" s="128"/>
+      <c r="BR25" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="BS25" s="143"/>
-      <c r="BT25" s="142" t="s">
+      <c r="BS25" s="128"/>
+      <c r="BT25" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="BU25" s="143"/>
-      <c r="BV25" s="142" t="s">
+      <c r="BU25" s="128"/>
+      <c r="BV25" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="BW25" s="143"/>
+      <c r="BW25" s="128"/>
       <c r="BY25" s="4" t="s">
         <v>4</v>
       </c>
@@ -11853,15 +11769,15 @@
       </c>
       <c r="CA25" s="13">
         <f t="shared" si="20"/>
-        <v>6.1764705882352944E-2</v>
+        <v>6.1904761904761914E-2</v>
       </c>
       <c r="CB25" s="13">
         <f t="shared" si="20"/>
-        <v>1.5126050420168062E-2</v>
+        <v>9.3506493506493524E-2</v>
       </c>
       <c r="CC25" s="13">
         <f t="shared" si="20"/>
-        <v>0.31134453781512611</v>
+        <v>0.24761904761904768</v>
       </c>
       <c r="CD25" s="13">
         <f t="shared" si="20"/>
@@ -11869,7 +11785,7 @@
       </c>
       <c r="CE25" s="13">
         <f t="shared" si="20"/>
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CF25" s="13">
         <f t="shared" si="20"/>
@@ -11877,7 +11793,7 @@
       </c>
       <c r="CG25" s="13">
         <f t="shared" si="20"/>
-        <v>9.3939393939393934E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="26" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11932,19 +11848,19 @@
       <c r="R26" s="23">
         <v>0</v>
       </c>
-      <c r="T26" s="99" t="s">
+      <c r="T26" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="U26" s="96"/>
-      <c r="V26" s="96"/>
-      <c r="W26" s="96"/>
-      <c r="X26" s="96"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="96"/>
-      <c r="AA26" s="96"/>
-      <c r="AB26" s="96"/>
-      <c r="AC26" s="96"/>
-      <c r="AD26" s="97"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="95"/>
+      <c r="AA26" s="95"/>
+      <c r="AB26" s="95"/>
+      <c r="AC26" s="95"/>
+      <c r="AD26" s="96"/>
       <c r="AL26" s="39" t="s">
         <v>9</v>
       </c>
@@ -11960,7 +11876,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP26" s="80">
+      <c r="AP26" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12069,15 +11985,15 @@
       </c>
       <c r="CA26" s="13">
         <f t="shared" si="20"/>
-        <v>6.1764705882352944E-2</v>
+        <v>6.1904761904761914E-2</v>
       </c>
       <c r="CB26" s="13">
         <f t="shared" si="20"/>
-        <v>1.5126050420168062E-2</v>
+        <v>9.3506493506493524E-2</v>
       </c>
       <c r="CC26" s="13">
         <f t="shared" si="20"/>
-        <v>0.31134453781512611</v>
+        <v>0.24761904761904768</v>
       </c>
       <c r="CD26" s="13">
         <f t="shared" si="20"/>
@@ -12085,7 +12001,7 @@
       </c>
       <c r="CE26" s="13">
         <f t="shared" si="20"/>
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CF26" s="13">
         <f t="shared" si="20"/>
@@ -12093,7 +12009,7 @@
       </c>
       <c r="CG26" s="13">
         <f t="shared" si="20"/>
-        <v>9.3939393939393934E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="27" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12148,31 +12064,31 @@
       <c r="R27" s="23">
         <v>2</v>
       </c>
-      <c r="T27" s="99" t="s">
+      <c r="T27" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="U27" s="96">
+      <c r="U27" s="95">
         <f>MAX(U4:U8)</f>
         <v>9</v>
       </c>
-      <c r="V27" s="96">
+      <c r="V27" s="95">
         <f>MAX(V16:V19)</f>
         <v>96</v>
       </c>
-      <c r="W27" s="96">
+      <c r="W27" s="95">
         <f>MAX(W18:W19)</f>
         <v>26</v>
       </c>
-      <c r="X27" s="96">
+      <c r="X27" s="95">
         <f>MAX(X4:X13)</f>
         <v>1</v>
       </c>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="96"/>
-      <c r="AA27" s="96"/>
-      <c r="AB27" s="96"/>
-      <c r="AC27" s="96"/>
-      <c r="AD27" s="97"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="95"/>
+      <c r="AD27" s="96"/>
       <c r="AL27" s="39" t="s">
         <v>10</v>
       </c>
@@ -12188,7 +12104,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP27" s="80">
+      <c r="AP27" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12299,15 +12215,15 @@
       </c>
       <c r="CA27" s="13">
         <f t="shared" si="20"/>
-        <v>8.9452332657200803E-2</v>
+        <v>8.9655172413793102E-2</v>
       </c>
       <c r="CB27" s="13">
         <f t="shared" si="20"/>
-        <v>1.3995943204868147E-2</v>
+        <v>8.6520376175548586E-2</v>
       </c>
       <c r="CC27" s="13">
         <f t="shared" si="20"/>
-        <v>0.30060851926977689</v>
+        <v>0.23908045977011499</v>
       </c>
       <c r="CD27" s="13">
         <f t="shared" si="20"/>
@@ -12315,7 +12231,7 @@
       </c>
       <c r="CE27" s="13">
         <f t="shared" si="20"/>
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CF27" s="13">
         <f t="shared" si="20"/>
@@ -12323,7 +12239,7 @@
       </c>
       <c r="CG27" s="13">
         <f t="shared" si="20"/>
-        <v>9.3939393939393934E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="28" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12378,31 +12294,31 @@
       <c r="R28" s="23">
         <v>0</v>
       </c>
-      <c r="T28" s="99" t="s">
-        <v>37</v>
-      </c>
-      <c r="U28" s="96">
+      <c r="T28" s="98" t="s">
+        <v>107</v>
+      </c>
+      <c r="U28" s="95">
         <f>MAX(U9:U14)</f>
         <v>28</v>
       </c>
-      <c r="V28" s="96">
+      <c r="V28" s="95">
         <f>MAX(V9:V15)</f>
         <v>66</v>
       </c>
-      <c r="W28" s="96">
+      <c r="W28" s="95">
         <f>MAX(W16:W17)</f>
         <v>8</v>
       </c>
-      <c r="X28" s="96">
+      <c r="X28" s="95">
         <f>MAX(X14:X15)</f>
         <v>5</v>
       </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="96"/>
-      <c r="AA28" s="96"/>
-      <c r="AB28" s="96"/>
-      <c r="AC28" s="96"/>
-      <c r="AD28" s="97"/>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="95"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="95"/>
+      <c r="AC28" s="95"/>
+      <c r="AD28" s="96"/>
       <c r="AL28" s="39" t="s">
         <v>11</v>
       </c>
@@ -12418,7 +12334,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="80">
+      <c r="AP28" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -12529,15 +12445,15 @@
       </c>
       <c r="CA28" s="13">
         <f t="shared" si="20"/>
-        <v>6.1764705882352944E-2</v>
+        <v>6.1904761904761914E-2</v>
       </c>
       <c r="CB28" s="13">
-        <f t="shared" si="20"/>
-        <v>1.5126050420168062E-2</v>
+        <f>BR32*BR$24</f>
+        <v>9.3506493506493524E-2</v>
       </c>
       <c r="CC28" s="13">
         <f t="shared" si="20"/>
-        <v>0.31134453781512611</v>
+        <v>0.24761904761904768</v>
       </c>
       <c r="CD28" s="13">
         <f t="shared" si="20"/>
@@ -12545,7 +12461,7 @@
       </c>
       <c r="CE28" s="13">
         <f t="shared" si="20"/>
-        <v>0.13749999999999998</v>
+        <v>6.8749999999999992E-2</v>
       </c>
       <c r="CF28" s="13">
         <f t="shared" si="20"/>
@@ -12553,7 +12469,7 @@
       </c>
       <c r="CG28" s="13">
         <f t="shared" si="20"/>
-        <v>0.12916666666666668</v>
+        <v>0.11458333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12608,31 +12524,31 @@
       <c r="R29" s="23">
         <v>0</v>
       </c>
-      <c r="T29" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="U29" s="96">
+      <c r="T29" s="98" t="s">
+        <v>37</v>
+      </c>
+      <c r="U29" s="95">
         <f>MAX(U15:U19)</f>
         <v>116</v>
       </c>
-      <c r="V29" s="96">
+      <c r="V29" s="95">
         <f>MAX(V4:V8)</f>
         <v>38</v>
       </c>
-      <c r="W29" s="96">
+      <c r="W29" s="95">
         <f>MAX(W4:W15)</f>
         <v>3</v>
       </c>
-      <c r="X29" s="96">
+      <c r="X29" s="95">
         <f>MAX(X16:X19)</f>
         <v>9</v>
       </c>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="96"/>
-      <c r="AA29" s="96"/>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-      <c r="AD29" s="97"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="95"/>
+      <c r="AB29" s="95"/>
+      <c r="AC29" s="95"/>
+      <c r="AD29" s="96"/>
       <c r="AL29" s="39" t="s">
         <v>12</v>
       </c>
@@ -12648,7 +12564,7 @@
         <f t="shared" si="2"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="AP29" s="80">
+      <c r="AP29" s="79">
         <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
@@ -12759,15 +12675,15 @@
       </c>
       <c r="CA29" s="13">
         <f t="shared" si="20"/>
-        <v>8.9452332657200803E-2</v>
+        <v>8.9655172413793102E-2</v>
       </c>
       <c r="CB29" s="13">
         <f t="shared" si="20"/>
-        <v>1.3995943204868147E-2</v>
+        <v>8.6520376175548586E-2</v>
       </c>
       <c r="CC29" s="13">
         <f t="shared" si="20"/>
-        <v>0.30060851926977689</v>
+        <v>0.23908045977011499</v>
       </c>
       <c r="CD29" s="13">
         <f t="shared" si="20"/>
@@ -12775,7 +12691,7 @@
       </c>
       <c r="CE29" s="13">
         <f t="shared" si="20"/>
-        <v>9.1666666666666674E-2</v>
+        <v>4.5833333333333337E-2</v>
       </c>
       <c r="CF29" s="13">
         <f t="shared" si="20"/>
@@ -12783,7 +12699,7 @@
       </c>
       <c r="CG29" s="13">
         <f t="shared" si="20"/>
-        <v>0.25833333333333336</v>
+        <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="30" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12838,17 +12754,17 @@
       <c r="R30" s="23">
         <v>0</v>
       </c>
-      <c r="T30" s="99"/>
-      <c r="U30" s="96"/>
-      <c r="V30" s="96"/>
-      <c r="W30" s="96"/>
-      <c r="X30" s="96"/>
-      <c r="Y30" s="96"/>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="96"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-      <c r="AD30" s="97"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="95"/>
+      <c r="V30" s="95"/>
+      <c r="W30" s="95"/>
+      <c r="X30" s="95"/>
+      <c r="Y30" s="95"/>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="95"/>
+      <c r="AC30" s="95"/>
+      <c r="AD30" s="96"/>
       <c r="AL30" s="39" t="s">
         <v>13</v>
       </c>
@@ -12864,7 +12780,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP30" s="80">
+      <c r="AP30" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12971,19 +12887,19 @@
       </c>
       <c r="BZ30" s="13">
         <f t="shared" si="20"/>
-        <v>1.0034602076124567E-2</v>
+        <v>1.2032085561497326E-2</v>
       </c>
       <c r="CA30" s="13">
         <f t="shared" si="20"/>
-        <v>0.22889273356401382</v>
+        <v>0.22941176470588237</v>
       </c>
       <c r="CB30" s="13">
         <f t="shared" si="20"/>
-        <v>8.8235294117647023E-3</v>
+        <v>5.454545454545455E-2</v>
       </c>
       <c r="CC30" s="13">
         <f t="shared" si="20"/>
-        <v>0.24653979238754328</v>
+        <v>0.19607843137254907</v>
       </c>
       <c r="CD30" s="13">
         <f t="shared" si="20"/>
@@ -12991,15 +12907,15 @@
       </c>
       <c r="CE30" s="13">
         <f t="shared" si="20"/>
-        <v>9.8717948717948728E-2</v>
+        <v>4.9358974358974364E-2</v>
       </c>
       <c r="CF30" s="13">
         <f t="shared" si="20"/>
-        <v>1.0256410256410253E-2</v>
+        <v>2.3076923076923075E-2</v>
       </c>
       <c r="CG30" s="13">
         <f t="shared" si="20"/>
-        <v>0.23846153846153853</v>
+        <v>0.21153846153846159</v>
       </c>
     </row>
     <row r="31" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13054,19 +12970,19 @@
       <c r="R31" s="23">
         <v>0</v>
       </c>
-      <c r="T31" s="99" t="s">
+      <c r="T31" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="U31" s="96"/>
-      <c r="V31" s="96"/>
-      <c r="W31" s="96"/>
-      <c r="X31" s="96"/>
-      <c r="Y31" s="96"/>
-      <c r="Z31" s="96"/>
-      <c r="AA31" s="96"/>
-      <c r="AB31" s="96"/>
-      <c r="AC31" s="96"/>
-      <c r="AD31" s="97"/>
+      <c r="U31" s="95"/>
+      <c r="V31" s="95"/>
+      <c r="W31" s="95"/>
+      <c r="X31" s="95"/>
+      <c r="Y31" s="95"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="95"/>
+      <c r="AB31" s="95"/>
+      <c r="AC31" s="95"/>
+      <c r="AD31" s="96"/>
       <c r="AL31" s="39" t="s">
         <v>14</v>
       </c>
@@ -13082,7 +12998,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP31" s="80">
+      <c r="AP31" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -13197,11 +13113,11 @@
       </c>
       <c r="CB31" s="13">
         <f t="shared" si="20"/>
-        <v>1.7647058823529405E-2</v>
+        <v>0.1090909090909091</v>
       </c>
       <c r="CC31" s="13">
         <f t="shared" si="20"/>
-        <v>0.33529411764705885</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="CD31" s="13">
         <f t="shared" si="20"/>
@@ -13209,7 +13125,7 @@
       </c>
       <c r="CE31" s="13">
         <f t="shared" si="20"/>
-        <v>0.18333333333333335</v>
+        <v>9.1666666666666674E-2</v>
       </c>
       <c r="CF31" s="13">
         <f t="shared" si="20"/>
@@ -13272,29 +13188,29 @@
       <c r="R32" s="23">
         <v>2</v>
       </c>
-      <c r="T32" s="99"/>
-      <c r="U32" s="96">
-        <f>(U27+U28+U24)</f>
-        <v>88</v>
-      </c>
-      <c r="V32" s="96">
-        <f t="shared" ref="V32:X32" si="21">(V27+V28+V24)</f>
-        <v>176</v>
-      </c>
-      <c r="W32" s="96">
+      <c r="T32" s="98"/>
+      <c r="U32" s="95">
+        <f>(U27+U29+U23)</f>
+        <v>135</v>
+      </c>
+      <c r="V32" s="95">
+        <f t="shared" ref="V32:X32" si="21">(V27+V29+V23)</f>
+        <v>174</v>
+      </c>
+      <c r="W32" s="95">
         <f t="shared" si="21"/>
-        <v>34</v>
-      </c>
-      <c r="X32" s="96">
+        <v>33</v>
+      </c>
+      <c r="X32" s="95">
         <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="105"/>
-      <c r="AA32" s="105"/>
-      <c r="AB32" s="105"/>
-      <c r="AC32" s="105"/>
-      <c r="AD32" s="106"/>
+      <c r="Y32" s="102"/>
+      <c r="Z32" s="103"/>
+      <c r="AA32" s="103"/>
+      <c r="AB32" s="103"/>
+      <c r="AC32" s="103"/>
+      <c r="AD32" s="104"/>
       <c r="AL32" s="39" t="s">
         <v>15</v>
       </c>
@@ -13310,7 +13226,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="80">
+      <c r="AP32" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -13417,19 +13333,19 @@
       </c>
       <c r="BZ32" s="13">
         <f t="shared" si="20"/>
-        <v>8.3213773314203734E-3</v>
+        <v>9.9778270509977823E-3</v>
       </c>
       <c r="CA32" s="13">
         <f t="shared" si="20"/>
-        <v>0.33744619799139164</v>
+        <v>0.33821138211382118</v>
       </c>
       <c r="CB32" s="13">
         <f t="shared" si="20"/>
-        <v>4.3041606886657082E-3</v>
+        <v>2.6607538802660754E-2</v>
       </c>
       <c r="CC32" s="13">
         <f t="shared" si="20"/>
-        <v>0.20444763271162125</v>
+        <v>0.16260162601626019</v>
       </c>
       <c r="CD32" s="13">
         <f t="shared" si="20"/>
@@ -13437,7 +13353,7 @@
       </c>
       <c r="CE32" s="13">
         <f t="shared" si="20"/>
-        <v>0.10312500000000001</v>
+        <v>5.1562500000000004E-2</v>
       </c>
       <c r="CF32" s="13">
         <f t="shared" si="20"/>
@@ -13445,7 +13361,7 @@
       </c>
       <c r="CG32" s="13">
         <f t="shared" si="20"/>
-        <v>0.22604166666666672</v>
+        <v>0.20052083333333337</v>
       </c>
     </row>
     <row r="33" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13500,16 +13416,16 @@
       <c r="R33" s="23">
         <v>4</v>
       </c>
-      <c r="T33" s="99"/>
-      <c r="U33" s="96"/>
-      <c r="V33" s="96"/>
-      <c r="W33" s="96"/>
-      <c r="X33" s="96"/>
-      <c r="Y33" s="107"/>
-      <c r="Z33" s="103" t="s">
+      <c r="T33" s="98"/>
+      <c r="U33" s="95"/>
+      <c r="V33" s="95"/>
+      <c r="W33" s="95"/>
+      <c r="X33" s="95"/>
+      <c r="Y33" s="105"/>
+      <c r="Z33" s="121" t="s">
         <v>133</v>
       </c>
-      <c r="AD33" s="108"/>
+      <c r="AD33" s="106"/>
       <c r="AL33" s="39" t="s">
         <v>16</v>
       </c>
@@ -13525,7 +13441,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP33" s="80">
+      <c r="AP33" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13636,15 +13552,15 @@
       </c>
       <c r="CA33" s="13">
         <f t="shared" si="20"/>
-        <v>8.9452332657200803E-2</v>
+        <v>8.9655172413793102E-2</v>
       </c>
       <c r="CB33" s="13">
         <f t="shared" si="20"/>
-        <v>1.3995943204868147E-2</v>
+        <v>8.6520376175548586E-2</v>
       </c>
       <c r="CC33" s="13">
         <f t="shared" si="20"/>
-        <v>0.30060851926977689</v>
+        <v>0.23908045977011499</v>
       </c>
       <c r="CD33" s="13">
         <f t="shared" si="20"/>
@@ -13652,7 +13568,7 @@
       </c>
       <c r="CE33" s="13">
         <f t="shared" si="20"/>
-        <v>0.11785714285714285</v>
+        <v>5.8928571428571427E-2</v>
       </c>
       <c r="CF33" s="13">
         <f t="shared" si="20"/>
@@ -13660,7 +13576,7 @@
       </c>
       <c r="CG33" s="13">
         <f t="shared" si="20"/>
-        <v>0.18452380952380953</v>
+        <v>0.16369047619047622</v>
       </c>
     </row>
     <row r="34" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13715,24 +13631,24 @@
       <c r="R34" s="23">
         <v>0</v>
       </c>
-      <c r="T34" s="99"/>
-      <c r="U34" s="100" t="s">
+      <c r="T34" s="98"/>
+      <c r="U34" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="V34" s="100" t="s">
+      <c r="V34" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="100" t="s">
+      <c r="W34" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="X34" s="112" t="s">
+      <c r="X34" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="Y34" s="107"/>
+      <c r="Y34" s="105"/>
       <c r="Z34" t="s">
         <v>134</v>
       </c>
-      <c r="AD34" s="108"/>
+      <c r="AD34" s="106"/>
       <c r="AL34" s="39" t="s">
         <v>17</v>
       </c>
@@ -13748,7 +13664,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP34" s="80">
+      <c r="AP34" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13859,15 +13775,15 @@
       </c>
       <c r="CA34" s="13">
         <f t="shared" si="20"/>
-        <v>3.202614379084967E-2</v>
+        <v>3.2098765432098768E-2</v>
       </c>
       <c r="CB34" s="13">
         <f t="shared" si="20"/>
-        <v>1.6339869281045742E-2</v>
+        <v>0.10101010101010101</v>
       </c>
       <c r="CC34" s="13">
         <f t="shared" si="20"/>
-        <v>0.32287581699346407</v>
+        <v>0.25679012345679014</v>
       </c>
       <c r="CD34" s="13">
         <f t="shared" si="20"/>
@@ -13875,7 +13791,7 @@
       </c>
       <c r="CE34" s="13">
         <f t="shared" si="20"/>
-        <v>0.11</v>
+        <v>5.5E-2</v>
       </c>
       <c r="CF34" s="13">
         <f t="shared" si="20"/>
@@ -13883,26 +13799,26 @@
       </c>
       <c r="CG34" s="13">
         <f t="shared" si="20"/>
-        <v>0.20666666666666669</v>
+        <v>0.18333333333333335</v>
       </c>
     </row>
     <row r="35" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="75">
-        <v>0</v>
-      </c>
-      <c r="D35" s="75">
-        <v>0</v>
-      </c>
-      <c r="E35" s="75">
-        <v>0</v>
-      </c>
-      <c r="F35" s="76">
+      <c r="C35" s="74">
+        <v>0</v>
+      </c>
+      <c r="D35" s="74">
+        <v>0</v>
+      </c>
+      <c r="E35" s="74">
+        <v>0</v>
+      </c>
+      <c r="F35" s="75">
         <v>0</v>
       </c>
       <c r="H35" s="39" t="s">
@@ -13938,43 +13854,43 @@
       <c r="R35" s="23">
         <v>0</v>
       </c>
-      <c r="T35" s="15" t="s">
+      <c r="T35" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="U35" s="56">
+      <c r="U35" s="141">
         <f>U22/U$32</f>
-        <v>2.2727272727272728E-2</v>
-      </c>
-      <c r="V35" s="56">
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="V35" s="141">
         <f>V22/V$32</f>
-        <v>0.39772727272727271</v>
-      </c>
-      <c r="W35" s="56">
+        <v>0.40229885057471265</v>
+      </c>
+      <c r="W35" s="141">
         <f>W22/W$32</f>
-        <v>0.44117647058823528</v>
-      </c>
-      <c r="X35" s="56">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="X35" s="141">
         <f>X22/X$32</f>
         <v>0</v>
       </c>
-      <c r="Y35" s="107"/>
-      <c r="AD35" s="108"/>
+      <c r="Y35" s="105"/>
+      <c r="AD35" s="106"/>
       <c r="AL35" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AM35" s="81">
+      <c r="AM35" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN35" s="82">
+      <c r="AN35" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="82">
+      <c r="AO35" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="83">
+      <c r="AP35" s="82">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -14085,15 +14001,15 @@
       </c>
       <c r="CA35" s="13">
         <f t="shared" si="20"/>
-        <v>8.9452332657200803E-2</v>
+        <v>8.9655172413793102E-2</v>
       </c>
       <c r="CB35" s="13">
         <f t="shared" si="20"/>
-        <v>1.3995943204868147E-2</v>
+        <v>8.6520376175548586E-2</v>
       </c>
       <c r="CC35" s="13">
         <f t="shared" si="20"/>
-        <v>0.30060851926977689</v>
+        <v>0.23908045977011499</v>
       </c>
       <c r="CD35" s="13">
         <f t="shared" si="20"/>
@@ -14101,7 +14017,7 @@
       </c>
       <c r="CE35" s="13">
         <f t="shared" si="20"/>
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CF35" s="13">
         <f t="shared" si="20"/>
@@ -14109,26 +14025,26 @@
       </c>
       <c r="CG35" s="13">
         <f t="shared" si="20"/>
-        <v>9.3939393939393934E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="36" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="71">
+      <c r="B36" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="70">
         <v>144</v>
       </c>
-      <c r="D36" s="71">
+      <c r="D36" s="70">
         <v>51</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="70">
         <v>6</v>
       </c>
-      <c r="F36" s="72">
+      <c r="F36" s="71">
         <v>2</v>
       </c>
       <c r="H36" s="39" t="s">
@@ -14164,24 +14080,24 @@
       <c r="R36" s="23">
         <v>1</v>
       </c>
-      <c r="T36" s="16"/>
-      <c r="U36" s="37">
+      <c r="T36" s="98"/>
+      <c r="U36" s="142">
         <f>U27/U$32</f>
-        <v>0.10227272727272728</v>
-      </c>
-      <c r="V36" s="37">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="V36" s="142">
         <f>V27/V$32</f>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="W36" s="37">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="W36" s="142">
         <f>W27/W$32</f>
-        <v>0.76470588235294112</v>
-      </c>
-      <c r="X36" s="37">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="X36" s="142">
         <f>X27/X$32</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="Y36" s="107"/>
+      <c r="Y36" s="105"/>
       <c r="Z36" s="16"/>
       <c r="AA36" s="7" t="s">
         <v>64</v>
@@ -14192,25 +14108,25 @@
       <c r="AC36" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="AD36" s="113" t="s">
+      <c r="AD36" s="111" t="s">
         <v>67</v>
       </c>
       <c r="AL36" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM36" s="87">
+      <c r="AM36" s="86">
         <f t="shared" ref="AM36:AM67" si="22">(AG$4-C36)/(AG$4-AG$5)</f>
         <v>0.53697749196141475</v>
       </c>
-      <c r="AN36" s="88">
+      <c r="AN36" s="87">
         <f t="shared" ref="AN36:AN67" si="23">(D36-AH$5)/(AH$4-AH$5)</f>
         <v>0.28813559322033899</v>
       </c>
-      <c r="AO36" s="88">
+      <c r="AO36" s="87">
         <f t="shared" ref="AO36:AO67" si="24">(E36-AI$5)/(AI$4-AI$5)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP36" s="89">
+      <c r="AP36" s="88">
         <f t="shared" ref="AP36:AP67" si="25">(AJ$4-F36)/(AJ$4-AJ$5)</f>
         <v>0.77777777777777779</v>
       </c>
@@ -14317,19 +14233,19 @@
       </c>
       <c r="BZ36" s="13">
         <f t="shared" si="20"/>
-        <v>8.5294117647058843E-3</v>
+        <v>1.0227272727272729E-2</v>
       </c>
       <c r="CA36" s="13">
         <f t="shared" si="20"/>
-        <v>0.3242647058823529</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="CB36" s="13">
         <f t="shared" si="20"/>
-        <v>4.8529411764705876E-3</v>
+        <v>3.0000000000000009E-2</v>
       </c>
       <c r="CC36" s="13">
         <f t="shared" si="20"/>
-        <v>0.20955882352941183</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="CD36" s="13">
         <f t="shared" si="20"/>
@@ -14337,15 +14253,15 @@
       </c>
       <c r="CE36" s="13">
         <f t="shared" si="20"/>
-        <v>8.0208333333333354E-2</v>
+        <v>4.0104166666666677E-2</v>
       </c>
       <c r="CF36" s="13">
         <f t="shared" si="20"/>
-        <v>8.3333333333333315E-3</v>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="CG36" s="13">
         <f t="shared" si="20"/>
-        <v>0.29062500000000002</v>
+        <v>0.2578125</v>
       </c>
     </row>
     <row r="37" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14400,43 +14316,43 @@
       <c r="R37" s="23">
         <v>0</v>
       </c>
-      <c r="T37" s="16" t="s">
+      <c r="T37" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="U37" s="37">
+      <c r="U37" s="142">
         <f>U23/U$32</f>
-        <v>0.11363636363636363</v>
-      </c>
-      <c r="V37" s="37">
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="V37" s="142">
         <f>V23/V$32</f>
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="W37" s="37">
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="W37" s="142">
         <f>W23/W$32</f>
-        <v>0.11764705882352941</v>
-      </c>
-      <c r="X37" s="37">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="X37" s="142">
         <f>X23/X$32</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="Y37" s="107"/>
+      <c r="Y37" s="105"/>
       <c r="Z37" s="15" t="s">
         <v>38</v>
       </c>
       <c r="AA37" s="56">
-        <f>MAX(0,U35-10%)</f>
-        <v>0</v>
+        <f>MAX(0,U35*0.9)</f>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="AB37" s="56">
-        <f>MAX(0,V35-10%)</f>
-        <v>0.29772727272727273</v>
+        <f t="shared" ref="AB37:AD37" si="26">MAX(0,V35*0.9)</f>
+        <v>0.36206896551724138</v>
       </c>
       <c r="AC37" s="56">
-        <f>MAX(0,W35-10%)</f>
-        <v>0.3411764705882353</v>
-      </c>
-      <c r="AD37" s="114">
-        <f>MAX(0,X35-10%)</f>
+        <f t="shared" si="26"/>
+        <v>0.40909090909090906</v>
+      </c>
+      <c r="AD37" s="112">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AL37" s="39" t="s">
@@ -14454,7 +14370,7 @@
         <f t="shared" si="24"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP37" s="80">
+      <c r="AP37" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -14565,15 +14481,15 @@
       </c>
       <c r="CA37" s="13">
         <f t="shared" si="20"/>
-        <v>3.202614379084967E-2</v>
+        <v>3.2098765432098768E-2</v>
       </c>
       <c r="CB37" s="13">
         <f t="shared" si="20"/>
-        <v>1.6339869281045742E-2</v>
+        <v>0.10101010101010101</v>
       </c>
       <c r="CC37" s="13">
         <f t="shared" si="20"/>
-        <v>0.32287581699346407</v>
+        <v>0.25679012345679014</v>
       </c>
       <c r="CD37" s="13">
         <f t="shared" si="20"/>
@@ -14581,7 +14497,7 @@
       </c>
       <c r="CE37" s="13">
         <f t="shared" si="20"/>
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CF37" s="13">
         <f t="shared" si="20"/>
@@ -14589,7 +14505,7 @@
       </c>
       <c r="CG37" s="13">
         <f t="shared" si="20"/>
-        <v>9.3939393939393934E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="38" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14644,40 +14560,40 @@
       <c r="R38" s="23">
         <v>2</v>
       </c>
-      <c r="T38" s="17"/>
-      <c r="U38" s="57">
+      <c r="T38" s="98"/>
+      <c r="U38" s="143">
         <f>U28/U$32</f>
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="V38" s="57">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="V38" s="143">
         <f>V28/V$32</f>
-        <v>0.375</v>
-      </c>
-      <c r="W38" s="57">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="W38" s="143">
         <f>W28/W$32</f>
-        <v>0.23529411764705882</v>
-      </c>
-      <c r="X38" s="57">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="X38" s="143">
         <f>X28/X$32</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="Y38" s="107"/>
+      <c r="Y38" s="105"/>
       <c r="Z38" s="16"/>
       <c r="AA38" s="37">
-        <f>MIN(1,U36+10%)</f>
-        <v>0.20227272727272727</v>
+        <f>MIN(1,U36*1.1)</f>
+        <v>7.3333333333333334E-2</v>
       </c>
       <c r="AB38" s="37">
-        <f>MIN(1,V36+10%)</f>
-        <v>0.64545454545454539</v>
+        <f t="shared" ref="AB38:AD38" si="27">MIN(1,V36*1.1)</f>
+        <v>0.60689655172413792</v>
       </c>
       <c r="AC38" s="37">
-        <f>MIN(1,W36+10%)</f>
-        <v>0.8647058823529411</v>
-      </c>
-      <c r="AD38" s="115">
-        <f>MIN(1,X36+10%)</f>
-        <v>0.18333333333333335</v>
+        <f t="shared" si="27"/>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AD38" s="113">
+        <f t="shared" si="27"/>
+        <v>9.1666666666666674E-2</v>
       </c>
       <c r="AL38" s="39" t="s">
         <v>4</v>
@@ -14694,7 +14610,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP38" s="80">
+      <c r="AP38" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -14805,15 +14721,15 @@
       </c>
       <c r="CA38" s="13">
         <f t="shared" si="20"/>
-        <v>0.20346020761245673</v>
+        <v>0.20392156862745098</v>
       </c>
       <c r="CB38" s="13">
         <f t="shared" si="20"/>
-        <v>9.3425605536332137E-3</v>
+        <v>5.7754010695187173E-2</v>
       </c>
       <c r="CC38" s="13">
         <f t="shared" si="20"/>
-        <v>0.25640138408304497</v>
+        <v>0.20392156862745101</v>
       </c>
       <c r="CD38" s="13">
         <f t="shared" si="20"/>
@@ -14821,7 +14737,7 @@
       </c>
       <c r="CE38" s="13">
         <f t="shared" si="20"/>
-        <v>0.16500000000000001</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="CF38" s="13">
         <f t="shared" si="20"/>
@@ -14829,7 +14745,7 @@
       </c>
       <c r="CG38" s="13">
         <f t="shared" si="20"/>
-        <v>5.1666666666666687E-2</v>
+        <v>4.5833333333333351E-2</v>
       </c>
     </row>
     <row r="39" spans="1:85" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14884,28 +14800,32 @@
       <c r="R39" s="23">
         <v>0</v>
       </c>
-      <c r="T39" s="16" t="s">
+      <c r="T39" s="102" t="s">
         <v>121</v>
       </c>
-      <c r="Y39" s="107"/>
+      <c r="U39" s="103"/>
+      <c r="V39" s="103"/>
+      <c r="W39" s="103"/>
+      <c r="X39" s="104"/>
+      <c r="Y39" s="105"/>
       <c r="Z39" s="16" t="s">
         <v>39</v>
       </c>
       <c r="AA39" s="37">
-        <f>MAX(0,U37-10%)</f>
-        <v>1.3636363636363627E-2</v>
+        <f>MAX(0,U37*0.9)</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="AB39" s="37">
-        <f>MAX(0,V37-10%)</f>
-        <v>0.12727272727272726</v>
+        <f t="shared" ref="AB39:AD39" si="28">MAX(0,V37*0.9)</f>
+        <v>0.20689655172413793</v>
       </c>
       <c r="AC39" s="37">
-        <f>MAX(0,W37-10%)</f>
-        <v>1.7647058823529405E-2</v>
-      </c>
-      <c r="AD39" s="115">
-        <f>MAX(0,X37-10%)</f>
-        <v>6.6666666666666652E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="AD39" s="113">
+        <f t="shared" si="28"/>
+        <v>0.15</v>
       </c>
       <c r="AL39" s="39" t="s">
         <v>5</v>
@@ -14922,7 +14842,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP39" s="80">
+      <c r="AP39" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -14960,21 +14880,21 @@
         <v>0</v>
       </c>
       <c r="BC39" s="45"/>
-      <c r="BD39" s="148" t="s">
+      <c r="BD39" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="BE39" s="150" t="s">
+      <c r="BE39" s="135" t="s">
         <v>111</v>
       </c>
-      <c r="BF39" s="150"/>
-      <c r="BG39" s="150"/>
-      <c r="BH39" s="150"/>
-      <c r="BI39" s="150" t="s">
+      <c r="BF39" s="135"/>
+      <c r="BG39" s="135"/>
+      <c r="BH39" s="135"/>
+      <c r="BI39" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="BJ39" s="150"/>
-      <c r="BK39" s="150"/>
-      <c r="BL39" s="151"/>
+      <c r="BJ39" s="135"/>
+      <c r="BK39" s="135"/>
+      <c r="BL39" s="136"/>
       <c r="BM39" s="45"/>
       <c r="BN39" s="45"/>
       <c r="BO39" s="4" t="s">
@@ -15057,40 +14977,40 @@
       <c r="R40" s="23">
         <v>0</v>
       </c>
-      <c r="T40" s="16"/>
-      <c r="U40" s="13">
-        <f>1+(U35+U36)/2-(U37+U38)/2</f>
-        <v>0.84659090909090906</v>
-      </c>
-      <c r="V40" s="13">
-        <f>1+(V35+V36)/2-(V37+V38)/2</f>
-        <v>1.1704545454545454</v>
-      </c>
-      <c r="W40" s="13">
-        <f>1+(W35+W36)/2-(W37+W38)/2</f>
-        <v>1.4264705882352942</v>
-      </c>
-      <c r="X40" s="13">
-        <f>1+(X35+X36)/2-(X37+X38)/2</f>
-        <v>0.75</v>
-      </c>
-      <c r="Y40" s="107"/>
+      <c r="T40" s="105"/>
+      <c r="U40" s="138">
+        <f>1+(AA37+AA38)/2-(AA39+AA40)/2</f>
+        <v>0.89592592592592601</v>
+      </c>
+      <c r="V40" s="138">
+        <f t="shared" ref="V40:X40" si="29">1+(AB37+AB38)/2-(AB39+AB40)/2</f>
+        <v>1.1724137931034484</v>
+      </c>
+      <c r="W40" s="138">
+        <f t="shared" si="29"/>
+        <v>1.45</v>
+      </c>
+      <c r="X40" s="139">
+        <f t="shared" si="29"/>
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="Y40" s="105"/>
       <c r="Z40" s="17"/>
       <c r="AA40" s="57">
-        <f>MIN(1,U38+10%)</f>
-        <v>0.41818181818181821</v>
+        <f>MIN(1,U38*1.1)</f>
+        <v>0.22814814814814816</v>
       </c>
       <c r="AB40" s="57">
-        <f>MIN(1,V38+10%)</f>
-        <v>0.47499999999999998</v>
+        <f t="shared" ref="AB40:AD40" si="30">MIN(1,V38*1.1)</f>
+        <v>0.41724137931034483</v>
       </c>
       <c r="AC40" s="57">
-        <f>MIN(1,W38+10%)</f>
-        <v>0.33529411764705885</v>
-      </c>
-      <c r="AD40" s="116">
-        <f>MIN(1,X38+10%)</f>
-        <v>0.51666666666666672</v>
+        <f t="shared" si="30"/>
+        <v>0.26666666666666672</v>
+      </c>
+      <c r="AD40" s="114">
+        <f t="shared" si="30"/>
+        <v>0.45833333333333337</v>
       </c>
       <c r="AL40" s="39" t="s">
         <v>6</v>
@@ -15107,7 +15027,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP40" s="80">
+      <c r="AP40" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -15145,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="BC40" s="45"/>
-      <c r="BD40" s="149"/>
+      <c r="BD40" s="134"/>
       <c r="BE40" s="47" t="s">
         <v>64</v>
       </c>
@@ -15252,20 +15172,20 @@
       <c r="R41" s="23">
         <v>1</v>
       </c>
-      <c r="T41" s="58">
+      <c r="T41" s="137">
         <f>SUM(U40:X40)/2</f>
-        <v>2.0967580213903743</v>
-      </c>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="109"/>
-      <c r="Z41" s="110"/>
-      <c r="AA41" s="110"/>
-      <c r="AB41" s="110"/>
-      <c r="AC41" s="110"/>
-      <c r="AD41" s="111"/>
+        <v>2.1300031928480205</v>
+      </c>
+      <c r="U41" s="108"/>
+      <c r="V41" s="108"/>
+      <c r="W41" s="108"/>
+      <c r="X41" s="109"/>
+      <c r="Y41" s="107"/>
+      <c r="Z41" s="108"/>
+      <c r="AA41" s="108"/>
+      <c r="AB41" s="108"/>
+      <c r="AC41" s="108"/>
+      <c r="AD41" s="109"/>
       <c r="AL41" s="39" t="s">
         <v>8</v>
       </c>
@@ -15281,7 +15201,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP41" s="80">
+      <c r="AP41" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15323,35 +15243,35 @@
         <v>1</v>
       </c>
       <c r="BE41" s="13">
-        <f t="shared" ref="BE41:BH56" si="26">(1-BI5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BE41:BH56" si="31">(1-BI5)/(BI5+1-BE5)</f>
         <v>8.8691796008869041E-3</v>
       </c>
       <c r="BF41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.27777777777777785</v>
       </c>
       <c r="BG41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.64516129032258063</v>
       </c>
       <c r="BH41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI41" s="13">
-        <f t="shared" ref="BI41:BL56" si="27">(1-BE5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BI41:BL56" si="32">(1-BE5)/(BI5+1-BE5)</f>
         <v>0.31929046563192903</v>
       </c>
       <c r="BJ41" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.57539682539682546</v>
       </c>
       <c r="BK41" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.80645161290322587</v>
       </c>
       <c r="BL41" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.25</v>
       </c>
       <c r="BM41" s="45"/>
@@ -15451,7 +15371,7 @@
         <f t="shared" si="24"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP42" s="80">
+      <c r="AP42" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15493,35 +15413,35 @@
         <v>2</v>
       </c>
       <c r="BE42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BF42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.1103678929765886</v>
       </c>
       <c r="BG42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BH42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>6.3897763578275226E-3</v>
       </c>
       <c r="BJ42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.51839464882943143</v>
       </c>
       <c r="BK42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.48000000000000004</v>
       </c>
       <c r="BL42" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="BM42" s="45"/>
@@ -15603,7 +15523,7 @@
       <c r="Q43" s="5">
         <v>4</v>
       </c>
-      <c r="R43" s="101">
+      <c r="R43" s="100">
         <v>6</v>
       </c>
       <c r="AL43" s="39" t="s">
@@ -15621,7 +15541,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP43" s="80">
+      <c r="AP43" s="79">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
@@ -15663,35 +15583,35 @@
         <v>4</v>
       </c>
       <c r="BE43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.010695187165772E-2</v>
       </c>
       <c r="BF43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.80208333333333326</v>
       </c>
       <c r="BG43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.20855614973262038</v>
       </c>
       <c r="BJ43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.88020833333333326</v>
       </c>
       <c r="BK43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL43" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM43" s="45"/>
@@ -15746,7 +15666,7 @@
       <c r="Q44" s="5">
         <v>0</v>
       </c>
-      <c r="R44" s="101">
+      <c r="R44" s="100">
         <v>0</v>
       </c>
       <c r="AL44" s="39" t="s">
@@ -15764,7 +15684,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP44" s="80">
+      <c r="AP44" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -15806,35 +15726,35 @@
         <v>5</v>
       </c>
       <c r="BE44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1.4705882352941131E-2</v>
       </c>
       <c r="BF44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.375</v>
       </c>
       <c r="BG44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.10000000000000002</v>
       </c>
       <c r="BJ44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.63750000000000007</v>
       </c>
       <c r="BK44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL44" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM44" s="45"/>
@@ -15889,7 +15809,7 @@
       <c r="Q45" s="5">
         <v>1</v>
       </c>
-      <c r="R45" s="101">
+      <c r="R45" s="100">
         <v>1</v>
       </c>
       <c r="AL45" s="39" t="s">
@@ -15907,7 +15827,7 @@
         <f t="shared" si="24"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP45" s="80">
+      <c r="AP45" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15949,35 +15869,35 @@
         <v>6</v>
       </c>
       <c r="BE45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>5.7471264367816119E-2</v>
       </c>
       <c r="BF45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.23605150214592274</v>
       </c>
       <c r="BG45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.16379310344827583</v>
       </c>
       <c r="BJ45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.47639484978540764</v>
       </c>
       <c r="BK45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL45" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM45" s="45"/>
@@ -16032,7 +15952,7 @@
       <c r="Q46" s="5">
         <v>2</v>
       </c>
-      <c r="R46" s="101">
+      <c r="R46" s="100">
         <v>5</v>
       </c>
       <c r="AL46" s="39" t="s">
@@ -16050,7 +15970,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP46" s="80">
+      <c r="AP46" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16092,35 +16012,35 @@
         <v>8</v>
       </c>
       <c r="BE46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>2.9498525073746323E-2</v>
       </c>
       <c r="BF46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.55825242718446599</v>
       </c>
       <c r="BG46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.11209439528023599</v>
       </c>
       <c r="BJ46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.69902912621359214</v>
       </c>
       <c r="BK46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL46" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.25</v>
       </c>
       <c r="BM46" s="45"/>
@@ -16175,7 +16095,7 @@
       <c r="Q47" s="5">
         <v>1</v>
       </c>
-      <c r="R47" s="101">
+      <c r="R47" s="100">
         <v>6</v>
       </c>
       <c r="AL47" s="39" t="s">
@@ -16193,7 +16113,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP47" s="80">
+      <c r="AP47" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16235,35 +16155,35 @@
         <v>9</v>
       </c>
       <c r="BE47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.9140049140049158E-2</v>
       </c>
       <c r="BF47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BG47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.28501228501228504</v>
       </c>
       <c r="BJ47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.46200607902735558</v>
       </c>
       <c r="BK47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL47" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.5</v>
       </c>
       <c r="BM47" s="45"/>
@@ -16318,7 +16238,7 @@
       <c r="Q48" s="5">
         <v>2</v>
       </c>
-      <c r="R48" s="101">
+      <c r="R48" s="100">
         <v>1</v>
       </c>
       <c r="AL48" s="39" t="s">
@@ -16336,7 +16256,7 @@
         <f t="shared" si="24"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP48" s="80">
+      <c r="AP48" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16378,35 +16298,35 @@
         <v>10</v>
       </c>
       <c r="BE48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>9.1346153846153855E-2</v>
       </c>
       <c r="BF48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.59605911330049266</v>
       </c>
       <c r="BG48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.5</v>
       </c>
       <c r="BH48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.15384615384615383</v>
       </c>
       <c r="BI48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.34375</v>
       </c>
       <c r="BJ48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.72413793103448276</v>
       </c>
       <c r="BK48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.73529411764705888</v>
       </c>
       <c r="BL48" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.46153846153846162</v>
       </c>
       <c r="BM48" s="45"/>
@@ -16461,7 +16381,7 @@
       <c r="Q49" s="5">
         <v>15</v>
       </c>
-      <c r="R49" s="101">
+      <c r="R49" s="100">
         <v>9</v>
       </c>
       <c r="AL49" s="39" t="s">
@@ -16479,7 +16399,7 @@
         <f t="shared" si="24"/>
         <v>0.53846153846153844</v>
       </c>
-      <c r="AP49" s="80">
+      <c r="AP49" s="79">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
@@ -16521,35 +16441,35 @@
         <v>11</v>
       </c>
       <c r="BE49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BF49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.29147982062780264</v>
       </c>
       <c r="BG49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="BH49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>9.5541401273885485E-3</v>
       </c>
       <c r="BJ49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.49775784753363228</v>
       </c>
       <c r="BK49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="BL49" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BM49" s="45"/>
@@ -16604,7 +16524,7 @@
       <c r="Q50" s="5">
         <v>1</v>
       </c>
-      <c r="R50" s="101">
+      <c r="R50" s="100">
         <v>0</v>
       </c>
       <c r="AL50" s="39" t="s">
@@ -16622,7 +16542,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP50" s="80">
+      <c r="AP50" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16664,35 +16584,35 @@
         <v>12</v>
       </c>
       <c r="BE50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1.4681892332789581E-2</v>
       </c>
       <c r="BF50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.44978165938864634</v>
       </c>
       <c r="BG50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="BH50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.5073409461663948</v>
       </c>
       <c r="BJ50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.67685589519650657</v>
       </c>
       <c r="BK50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.6097560975609756</v>
       </c>
       <c r="BL50" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.43750000000000006</v>
       </c>
       <c r="BM50" s="45"/>
@@ -16702,7 +16622,7 @@
       <c r="A51" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="59" t="s">
+      <c r="B51" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="24">
@@ -16720,7 +16640,7 @@
       <c r="H51" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="59" t="s">
+      <c r="I51" s="58" t="s">
         <v>119</v>
       </c>
       <c r="J51" s="24">
@@ -16735,7 +16655,7 @@
       <c r="M51" s="24">
         <v>0</v>
       </c>
-      <c r="N51" s="59" t="s">
+      <c r="N51" s="58" t="s">
         <v>120</v>
       </c>
       <c r="O51" s="24">
@@ -16747,25 +16667,25 @@
       <c r="Q51" s="24">
         <v>8</v>
       </c>
-      <c r="R51" s="102">
-        <v>1</v>
-      </c>
-      <c r="AL51" s="73" t="s">
+      <c r="R51" s="101">
+        <v>1</v>
+      </c>
+      <c r="AL51" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM51" s="84">
+      <c r="AM51" s="83">
         <f t="shared" si="22"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN51" s="85">
+      <c r="AN51" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO51" s="85">
+      <c r="AO51" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP51" s="86">
+      <c r="AP51" s="85">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -16775,31 +16695,31 @@
       <c r="AS51" s="18">
         <v>4</v>
       </c>
-      <c r="AT51" s="60">
-        <v>1</v>
-      </c>
-      <c r="AU51" s="60">
+      <c r="AT51" s="59">
+        <v>1</v>
+      </c>
+      <c r="AU51" s="59">
         <v>0.29943502824858759</v>
       </c>
-      <c r="AV51" s="60">
+      <c r="AV51" s="59">
         <v>0.73076923076923073</v>
       </c>
-      <c r="AW51" s="60">
+      <c r="AW51" s="59">
         <v>0</v>
       </c>
       <c r="AX51" s="18">
         <v>5</v>
       </c>
-      <c r="AY51" s="60">
+      <c r="AY51" s="59">
         <v>0.98713826366559487</v>
       </c>
-      <c r="AZ51" s="60">
+      <c r="AZ51" s="59">
         <v>0.5423728813559322</v>
       </c>
-      <c r="BA51" s="60">
+      <c r="BA51" s="59">
         <v>0.69230769230769229</v>
       </c>
-      <c r="BB51" s="61">
+      <c r="BB51" s="60">
         <v>0.1111111111111111</v>
       </c>
       <c r="BC51" s="45"/>
@@ -16807,35 +16727,35 @@
         <v>13</v>
       </c>
       <c r="BE51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>2.1604938271604934E-2</v>
       </c>
       <c r="BF51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.25523012552301261</v>
       </c>
       <c r="BG51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>6.1728395061728419E-2</v>
       </c>
       <c r="BJ51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.5146443514644351</v>
       </c>
       <c r="BK51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL51" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.35714285714285715</v>
       </c>
       <c r="BM51" s="45"/>
@@ -16864,19 +16784,19 @@
       <c r="AL52" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM52" s="77">
+      <c r="AM52" s="76">
         <f t="shared" si="22"/>
         <v>0.96784565916398713</v>
       </c>
-      <c r="AN52" s="78">
+      <c r="AN52" s="77">
         <f t="shared" si="23"/>
         <v>0.49717514124293788</v>
       </c>
-      <c r="AO52" s="78">
+      <c r="AO52" s="77">
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP52" s="79">
+      <c r="AP52" s="78">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -16885,35 +16805,35 @@
         <v>14</v>
       </c>
       <c r="BE52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>5.9659090909090898E-2</v>
       </c>
       <c r="BF52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.40092165898617516</v>
       </c>
       <c r="BG52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.17613636363636365</v>
       </c>
       <c r="BJ52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.58525345622119818</v>
       </c>
       <c r="BK52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.96296296296296291</v>
       </c>
       <c r="BL52" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.4</v>
       </c>
     </row>
@@ -16952,7 +16872,7 @@
         <f t="shared" si="24"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP53" s="80">
+      <c r="AP53" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -16961,35 +16881,35 @@
         <v>15</v>
       </c>
       <c r="BE53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>9.4339622641509569E-3</v>
       </c>
       <c r="BF53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.4358974358974359</v>
       </c>
       <c r="BG53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>3.1446540880503158E-2</v>
       </c>
       <c r="BJ53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.67948717948717952</v>
       </c>
       <c r="BK53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL53" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -17028,7 +16948,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP54" s="80">
+      <c r="AP54" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17037,35 +16957,35 @@
         <v>16</v>
       </c>
       <c r="BE54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>9.3596059113300503E-2</v>
       </c>
       <c r="BF54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.40350877192982459</v>
       </c>
       <c r="BG54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.27500000000000008</v>
       </c>
       <c r="BH54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.125</v>
       </c>
       <c r="BI54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.32758620689655171</v>
       </c>
       <c r="BJ54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.62719298245614041</v>
       </c>
       <c r="BK54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.62500000000000011</v>
       </c>
       <c r="BL54" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.5625</v>
       </c>
     </row>
@@ -17104,7 +17024,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP55" s="80">
+      <c r="AP55" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17113,35 +17033,35 @@
         <v>17</v>
       </c>
       <c r="BE55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1.2012012012011993E-2</v>
       </c>
       <c r="BF55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.56108597285067874</v>
       </c>
       <c r="BG55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>7.8078078078078109E-2</v>
       </c>
       <c r="BJ55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.7601809954751132</v>
       </c>
       <c r="BK55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.96296296296296291</v>
       </c>
       <c r="BL55" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -17180,7 +17100,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP56" s="80">
+      <c r="AP56" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17189,35 +17109,35 @@
         <v>21</v>
       </c>
       <c r="BE56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BF56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.2967032967032967</v>
       </c>
       <c r="BG56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.52941176470588236</v>
       </c>
       <c r="BH56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BI56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>1.2698412698412683E-2</v>
       </c>
       <c r="BJ56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.64835164835164838</v>
       </c>
       <c r="BK56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.76470588235294112</v>
       </c>
       <c r="BL56" s="55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.10000000000000003</v>
       </c>
     </row>
@@ -17256,7 +17176,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP57" s="80">
+      <c r="AP57" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17297,7 +17217,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP58" s="80">
+      <c r="AP58" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17338,7 +17258,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP59" s="80">
+      <c r="AP59" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -17379,7 +17299,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP60" s="80">
+      <c r="AP60" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17420,7 +17340,7 @@
         <f t="shared" si="24"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP61" s="80">
+      <c r="AP61" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17461,7 +17381,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP62" s="80">
+      <c r="AP62" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17502,7 +17422,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP63" s="80">
+      <c r="AP63" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17543,7 +17463,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP64" s="80">
+      <c r="AP64" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -17584,7 +17504,7 @@
         <f t="shared" si="24"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP65" s="80">
+      <c r="AP65" s="79">
         <f t="shared" si="25"/>
         <v>0.55555555555555558</v>
       </c>
@@ -17625,7 +17545,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP66" s="80">
+      <c r="AP66" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17666,49 +17586,49 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP67" s="80">
+      <c r="AP67" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="AR67" s="4"/>
     </row>
     <row r="68" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="75">
+      <c r="B68" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="74">
         <v>18</v>
       </c>
-      <c r="D68" s="75">
+      <c r="D68" s="74">
         <v>107</v>
       </c>
-      <c r="E68" s="75">
+      <c r="E68" s="74">
         <v>2</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="75">
         <v>3</v>
       </c>
       <c r="H68" s="4"/>
       <c r="AL68" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="AM68" s="81">
-        <f t="shared" ref="AM68:AM99" si="28">(AG$4-C68)/(AG$4-AG$5)</f>
+      <c r="AM68" s="80">
+        <f t="shared" ref="AM68:AM99" si="33">(AG$4-C68)/(AG$4-AG$5)</f>
         <v>0.94212218649517687</v>
       </c>
-      <c r="AN68" s="82">
-        <f t="shared" ref="AN68:AN99" si="29">(D68-AH$5)/(AH$4-AH$5)</f>
+      <c r="AN68" s="81">
+        <f t="shared" ref="AN68:AN99" si="34">(D68-AH$5)/(AH$4-AH$5)</f>
         <v>0.60451977401129942</v>
       </c>
-      <c r="AO68" s="82">
-        <f t="shared" ref="AO68:AO99" si="30">(E68-AI$5)/(AI$4-AI$5)</f>
+      <c r="AO68" s="81">
+        <f t="shared" ref="AO68:AO99" si="35">(E68-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP68" s="83">
-        <f t="shared" ref="AP68:AP99" si="31">(AJ$4-F68)/(AJ$4-AJ$5)</f>
+      <c r="AP68" s="82">
+        <f t="shared" ref="AP68:AP99" si="36">(AJ$4-F68)/(AJ$4-AJ$5)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR68" s="4"/>
@@ -17717,39 +17637,39 @@
       <c r="A69" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="70" t="s">
+      <c r="B69" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="71">
-        <v>1</v>
-      </c>
-      <c r="D69" s="71">
+      <c r="C69" s="70">
+        <v>1</v>
+      </c>
+      <c r="D69" s="70">
         <v>144</v>
       </c>
-      <c r="E69" s="71">
+      <c r="E69" s="70">
         <v>3</v>
       </c>
-      <c r="F69" s="72">
+      <c r="F69" s="71">
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
       <c r="AL69" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AM69" s="87">
-        <f t="shared" si="28"/>
+      <c r="AM69" s="86">
+        <f t="shared" si="33"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN69" s="88">
-        <f t="shared" si="29"/>
+      <c r="AN69" s="87">
+        <f t="shared" si="34"/>
         <v>0.81355932203389836</v>
       </c>
-      <c r="AO69" s="88">
-        <f t="shared" si="30"/>
+      <c r="AO69" s="87">
+        <f t="shared" si="35"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP69" s="89">
-        <f t="shared" si="31"/>
+      <c r="AP69" s="88">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR69" s="4"/>
@@ -17778,19 +17698,19 @@
         <v>4</v>
       </c>
       <c r="AM70" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="AN70" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="AO70" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP70" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP70" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR70" s="4"/>
@@ -17819,19 +17739,19 @@
         <v>5</v>
       </c>
       <c r="AM71" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.89389067524115751</v>
       </c>
       <c r="AN71" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="AO71" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP71" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP71" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR71" s="4"/>
@@ -17860,19 +17780,19 @@
         <v>6</v>
       </c>
       <c r="AM72" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.90353697749196138</v>
       </c>
       <c r="AN72" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.4463276836158192</v>
       </c>
       <c r="AO72" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP72" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP72" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR72" s="4"/>
@@ -17901,19 +17821,19 @@
         <v>8</v>
       </c>
       <c r="AM73" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="AN73" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="AO73" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP73" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP73" s="79">
+        <f t="shared" si="36"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR73" s="4"/>
@@ -17942,19 +17862,19 @@
         <v>9</v>
       </c>
       <c r="AM74" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.6463022508038585</v>
       </c>
       <c r="AN74" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AO74" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP74" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP74" s="79">
+        <f t="shared" si="36"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR74" s="4"/>
@@ -17983,19 +17903,19 @@
         <v>10</v>
       </c>
       <c r="AM75" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="AN75" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO75" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP75" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP75" s="79">
+        <f t="shared" si="36"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR75" s="4"/>
@@ -18024,19 +17944,19 @@
         <v>11</v>
       </c>
       <c r="AM76" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN76" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO76" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP76" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP76" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR76" s="4"/>
@@ -18065,19 +17985,19 @@
         <v>12</v>
       </c>
       <c r="AM77" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN77" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="AO77" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP77" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP77" s="79">
+        <f t="shared" si="36"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR77" s="4"/>
@@ -18106,19 +18026,19 @@
         <v>13</v>
       </c>
       <c r="AM78" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN78" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO78" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP78" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP78" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR78" s="4"/>
@@ -18147,19 +18067,19 @@
         <v>14</v>
       </c>
       <c r="AM79" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="AN79" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.38983050847457629</v>
       </c>
       <c r="AO79" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP79" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP79" s="79">
+        <f t="shared" si="36"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR79" s="4"/>
@@ -18188,19 +18108,19 @@
         <v>15</v>
       </c>
       <c r="AM80" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="AN80" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="AO80" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP80" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP80" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR80" s="4"/>
@@ -18229,19 +18149,19 @@
         <v>16</v>
       </c>
       <c r="AM81" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.6913183279742765</v>
       </c>
       <c r="AN81" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="AO81" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP81" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP81" s="79">
+        <f t="shared" si="36"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AR81" s="4"/>
@@ -18270,19 +18190,19 @@
         <v>17</v>
       </c>
       <c r="AM82" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="AN82" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="AO82" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP82" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP82" s="79">
+        <f t="shared" si="36"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR82" s="4"/>
@@ -18291,7 +18211,7 @@
       <c r="A83" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="59" t="s">
+      <c r="B83" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="24">
@@ -18307,23 +18227,23 @@
         <v>0</v>
       </c>
       <c r="H83" s="4"/>
-      <c r="AL83" s="73" t="s">
+      <c r="AL83" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM83" s="84">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AN83" s="85">
-        <f t="shared" si="29"/>
+      <c r="AM83" s="83">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="AN83" s="84">
+        <f t="shared" si="34"/>
         <v>0.29943502824858759</v>
       </c>
-      <c r="AO83" s="85">
-        <f t="shared" si="30"/>
+      <c r="AO83" s="84">
+        <f t="shared" si="35"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP83" s="86">
-        <f t="shared" si="31"/>
+      <c r="AP83" s="85">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR83" s="4"/>
@@ -18351,20 +18271,20 @@
       <c r="AL84" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM84" s="77">
-        <f t="shared" si="28"/>
+      <c r="AM84" s="76">
+        <f t="shared" si="33"/>
         <v>0.98392282958199362</v>
       </c>
-      <c r="AN84" s="78">
-        <f t="shared" si="29"/>
+      <c r="AN84" s="77">
+        <f t="shared" si="34"/>
         <v>0.39548022598870058</v>
       </c>
-      <c r="AO84" s="78">
-        <f t="shared" si="30"/>
+      <c r="AO84" s="77">
+        <f t="shared" si="35"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP84" s="79">
-        <f t="shared" si="31"/>
+      <c r="AP84" s="78">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR84" s="4"/>
@@ -18393,19 +18313,19 @@
         <v>2</v>
       </c>
       <c r="AM85" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.99356913183279738</v>
       </c>
       <c r="AN85" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.3559322033898305</v>
       </c>
       <c r="AO85" s="44">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="AP85" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="AP85" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR85" s="4"/>
@@ -18434,19 +18354,19 @@
         <v>4</v>
       </c>
       <c r="AM86" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN86" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>7.909604519774012E-2</v>
       </c>
       <c r="AO86" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP86" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP86" s="79">
+        <f t="shared" si="36"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR86" s="4"/>
@@ -18475,19 +18395,19 @@
         <v>5</v>
       </c>
       <c r="AM87" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN87" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO87" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP87" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP87" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR87" s="4"/>
@@ -18516,19 +18436,19 @@
         <v>6</v>
       </c>
       <c r="AM88" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.83601286173633438</v>
       </c>
       <c r="AN88" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="AO88" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP88" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP88" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR88" s="4"/>
@@ -18557,19 +18477,19 @@
         <v>8</v>
       </c>
       <c r="AM89" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN89" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="AO89" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP89" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP89" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR89" s="4"/>
@@ -18598,19 +18518,19 @@
         <v>9</v>
       </c>
       <c r="AM90" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="AN90" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.22598870056497175</v>
       </c>
       <c r="AO90" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP90" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP90" s="79">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AR90" s="4"/>
@@ -18639,19 +18559,19 @@
         <v>10</v>
       </c>
       <c r="AM91" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.65273311897106112</v>
       </c>
       <c r="AN91" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="AO91" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP91" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP91" s="79">
+        <f t="shared" si="36"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR91" s="4"/>
@@ -18680,19 +18600,19 @@
         <v>11</v>
       </c>
       <c r="AM92" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="AN92" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.40677966101694918</v>
       </c>
       <c r="AO92" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP92" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP92" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR92" s="4"/>
@@ -18721,19 +18641,19 @@
         <v>12</v>
       </c>
       <c r="AM93" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="AN93" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.21468926553672316</v>
       </c>
       <c r="AO93" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP93" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP93" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR93" s="4"/>
@@ -18762,19 +18682,19 @@
         <v>13</v>
       </c>
       <c r="AM94" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN94" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.33898305084745761</v>
       </c>
       <c r="AO94" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP94" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP94" s="79">
+        <f t="shared" si="36"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR94" s="4"/>
@@ -18803,19 +18723,19 @@
         <v>14</v>
       </c>
       <c r="AM95" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.83279742765273312</v>
       </c>
       <c r="AN95" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="AO95" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP95" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP95" s="79">
+        <f t="shared" si="36"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR95" s="4"/>
@@ -18844,19 +18764,19 @@
         <v>15</v>
       </c>
       <c r="AM96" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="AN96" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO96" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP96" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP96" s="79">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR96" s="4"/>
@@ -18885,19 +18805,19 @@
         <v>16</v>
       </c>
       <c r="AM97" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.74598070739549838</v>
       </c>
       <c r="AN97" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.29378531073446329</v>
       </c>
       <c r="AO97" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="AP97" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP97" s="79">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AR97" s="4"/>
@@ -18926,19 +18846,19 @@
         <v>17</v>
       </c>
       <c r="AM98" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0.96141479099678462</v>
       </c>
       <c r="AN98" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO98" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP98" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP98" s="79">
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AR98" s="4"/>
@@ -18947,7 +18867,7 @@
       <c r="A99" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="B99" s="59" t="s">
+      <c r="B99" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="24">
@@ -18966,20 +18886,20 @@
       <c r="AL99" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AM99" s="81">
-        <f t="shared" si="28"/>
+      <c r="AM99" s="80">
+        <f t="shared" si="33"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN99" s="82">
-        <f t="shared" si="29"/>
+      <c r="AN99" s="81">
+        <f t="shared" si="34"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="AO99" s="82">
-        <f t="shared" si="30"/>
+      <c r="AO99" s="81">
+        <f t="shared" si="35"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="AP99" s="83">
-        <f t="shared" si="31"/>
+      <c r="AP99" s="82">
+        <f t="shared" si="36"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR99" s="4"/>
